--- a/Shablon/TDS220.xlsx
+++ b/Shablon/TDS220.xlsx
@@ -17,12 +17,11 @@
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="152511"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="306">
   <si>
     <t>Допуск</t>
   </si>
@@ -513,13 +512,6 @@
     <t>∆Т</t>
   </si>
   <si>
-    <t>АО "Гос МКБ "Вымпел" им. И.И. Торопова"
-СГМетр, лаборатория средств электрорадиотехнических измерений
-125424, г.Москва, Волоколамское шоссе, дом 90, стр. 23
-Уникальный номер об аккредитации в реестре аккредитованных лиц № РОСС СОБ 3.00231.2014
-Тел.+7 (495) 491-05-31, 22-68, e-mail: ogmetr@vympelmkb.ru</t>
-  </si>
-  <si>
     <t xml:space="preserve">Наименование и тип СИ: </t>
   </si>
   <si>
@@ -654,66 +646,30 @@
     <t>dcv1_1</t>
   </si>
   <si>
-    <t>dcv1_2</t>
-  </si>
-  <si>
     <t>dcv1_3</t>
   </si>
   <si>
-    <t>dcv1_4</t>
-  </si>
-  <si>
-    <t>dcv1_5</t>
-  </si>
-  <si>
     <t>dcv1_6</t>
   </si>
   <si>
-    <t>dcv1_7</t>
-  </si>
-  <si>
-    <t>dcv1_8</t>
-  </si>
-  <si>
     <t>dcv1_9</t>
   </si>
   <si>
-    <t>dcv1_10</t>
-  </si>
-  <si>
     <t>dcv1_11</t>
   </si>
   <si>
     <t>dcv2_1</t>
   </si>
   <si>
-    <t>dcv2_2</t>
-  </si>
-  <si>
     <t>dcv2_3</t>
   </si>
   <si>
-    <t>dcv2_4</t>
-  </si>
-  <si>
-    <t>dcv2_5</t>
-  </si>
-  <si>
     <t>dcv2_6</t>
   </si>
   <si>
-    <t>dcv2_7</t>
-  </si>
-  <si>
-    <t>dcv2_8</t>
-  </si>
-  <si>
     <t>dcv2_9</t>
   </si>
   <si>
-    <t>dcv2_10</t>
-  </si>
-  <si>
     <t>dcv2_11</t>
   </si>
   <si>
@@ -733,90 +689,6 @@
   </si>
   <si>
     <t>tr2_3</t>
-  </si>
-  <si>
-    <t>t_1</t>
-  </si>
-  <si>
-    <t>t_2</t>
-  </si>
-  <si>
-    <t>t_3</t>
-  </si>
-  <si>
-    <t>t_4</t>
-  </si>
-  <si>
-    <t>t_5</t>
-  </si>
-  <si>
-    <t>t_6</t>
-  </si>
-  <si>
-    <t>t_7</t>
-  </si>
-  <si>
-    <t>t_8</t>
-  </si>
-  <si>
-    <t>t_9</t>
-  </si>
-  <si>
-    <t>t_10</t>
-  </si>
-  <si>
-    <t>t_11</t>
-  </si>
-  <si>
-    <t>t_12</t>
-  </si>
-  <si>
-    <t>t_13</t>
-  </si>
-  <si>
-    <t>t_14</t>
-  </si>
-  <si>
-    <t>t_15</t>
-  </si>
-  <si>
-    <t>t_16</t>
-  </si>
-  <si>
-    <t>t_17</t>
-  </si>
-  <si>
-    <t>t_18</t>
-  </si>
-  <si>
-    <t>t_19</t>
-  </si>
-  <si>
-    <t>t_20</t>
-  </si>
-  <si>
-    <t>t_21</t>
-  </si>
-  <si>
-    <t>t_22</t>
-  </si>
-  <si>
-    <t>t_23</t>
-  </si>
-  <si>
-    <t>t_24</t>
-  </si>
-  <si>
-    <t>t_25</t>
-  </si>
-  <si>
-    <t>t_26</t>
-  </si>
-  <si>
-    <t>t_27</t>
-  </si>
-  <si>
-    <t>t_28</t>
   </si>
   <si>
     <t>Заключение:</t>
@@ -873,13 +745,278 @@
       <t xml:space="preserve"> соответствует</t>
     </r>
   </si>
+  <si>
+    <t>dcv3_1</t>
+  </si>
+  <si>
+    <t>dcv3_3</t>
+  </si>
+  <si>
+    <t>dcv4_1</t>
+  </si>
+  <si>
+    <t>dcv4_3</t>
+  </si>
+  <si>
+    <t>tr3_1</t>
+  </si>
+  <si>
+    <t>tr4_1</t>
+  </si>
+  <si>
+    <t>tr3_2</t>
+  </si>
+  <si>
+    <t>tr3_3</t>
+  </si>
+  <si>
+    <t>tr4_2</t>
+  </si>
+  <si>
+    <t>tr4_3</t>
+  </si>
+  <si>
+    <t>gdcv1_1</t>
+  </si>
+  <si>
+    <t>gdcv1_2</t>
+  </si>
+  <si>
+    <t>gdcv1_3</t>
+  </si>
+  <si>
+    <t>gdcv1_4</t>
+  </si>
+  <si>
+    <t>gdcv1_5</t>
+  </si>
+  <si>
+    <t>gdcv1_6</t>
+  </si>
+  <si>
+    <t>gdcv1_7</t>
+  </si>
+  <si>
+    <t>gdcv1_8</t>
+  </si>
+  <si>
+    <t>gdcv1_9</t>
+  </si>
+  <si>
+    <t>gdcv1_10</t>
+  </si>
+  <si>
+    <t>gdcv1_11</t>
+  </si>
+  <si>
+    <t>gdcv2_1</t>
+  </si>
+  <si>
+    <t>gdcv3_1</t>
+  </si>
+  <si>
+    <t>gdcv4_1</t>
+  </si>
+  <si>
+    <t>gdcv2_2</t>
+  </si>
+  <si>
+    <t>gdcv3_2</t>
+  </si>
+  <si>
+    <t>gdcv4_2</t>
+  </si>
+  <si>
+    <t>gdcv2_3</t>
+  </si>
+  <si>
+    <t>gdcv3_3</t>
+  </si>
+  <si>
+    <t>gdcv4_3</t>
+  </si>
+  <si>
+    <t>gdcv2_4</t>
+  </si>
+  <si>
+    <t>gdcv3_4</t>
+  </si>
+  <si>
+    <t>gdcv4_4</t>
+  </si>
+  <si>
+    <t>gdcv2_5</t>
+  </si>
+  <si>
+    <t>gdcv3_5</t>
+  </si>
+  <si>
+    <t>gdcv4_5</t>
+  </si>
+  <si>
+    <t>gdcv2_6</t>
+  </si>
+  <si>
+    <t>gdcv3_6</t>
+  </si>
+  <si>
+    <t>gdcv4_6</t>
+  </si>
+  <si>
+    <t>gdcv2_7</t>
+  </si>
+  <si>
+    <t>gdcv3_7</t>
+  </si>
+  <si>
+    <t>gdcv4_7</t>
+  </si>
+  <si>
+    <t>gdcv2_8</t>
+  </si>
+  <si>
+    <t>gdcv3_8</t>
+  </si>
+  <si>
+    <t>gdcv4_8</t>
+  </si>
+  <si>
+    <t>gdcv2_9</t>
+  </si>
+  <si>
+    <t>gdcv3_9</t>
+  </si>
+  <si>
+    <t>gdcv4_9</t>
+  </si>
+  <si>
+    <t>gdcv2_10</t>
+  </si>
+  <si>
+    <t>gdcv3_10</t>
+  </si>
+  <si>
+    <t>gdcv4_10</t>
+  </si>
+  <si>
+    <t>gdcv2_11</t>
+  </si>
+  <si>
+    <t>gdcv3_11</t>
+  </si>
+  <si>
+    <t>gdcv4_11</t>
+  </si>
+  <si>
+    <t>dcv3_6</t>
+  </si>
+  <si>
+    <t>dcv3_9</t>
+  </si>
+  <si>
+    <t>dcv3_11</t>
+  </si>
+  <si>
+    <t>dcv4_6</t>
+  </si>
+  <si>
+    <t>dcv4_9</t>
+  </si>
+  <si>
+    <t>dcv4_11</t>
+  </si>
+  <si>
+    <t>t1_1</t>
+  </si>
+  <si>
+    <t>t1_2</t>
+  </si>
+  <si>
+    <t>t1_3</t>
+  </si>
+  <si>
+    <t>t1_4</t>
+  </si>
+  <si>
+    <t>t1_5</t>
+  </si>
+  <si>
+    <t>t1_6</t>
+  </si>
+  <si>
+    <t>t1_7</t>
+  </si>
+  <si>
+    <t>t1_8</t>
+  </si>
+  <si>
+    <t>t1_9</t>
+  </si>
+  <si>
+    <t>t1_10</t>
+  </si>
+  <si>
+    <t>t1_11</t>
+  </si>
+  <si>
+    <t>t1_12</t>
+  </si>
+  <si>
+    <t>t1_13</t>
+  </si>
+  <si>
+    <t>t1_14</t>
+  </si>
+  <si>
+    <t>t1_15</t>
+  </si>
+  <si>
+    <t>t1_16</t>
+  </si>
+  <si>
+    <t>t1_17</t>
+  </si>
+  <si>
+    <t>t1_18</t>
+  </si>
+  <si>
+    <t>t1_19</t>
+  </si>
+  <si>
+    <t>t1_20</t>
+  </si>
+  <si>
+    <t>t1_21</t>
+  </si>
+  <si>
+    <t>t1_22</t>
+  </si>
+  <si>
+    <t>t1_23</t>
+  </si>
+  <si>
+    <t>t1_24</t>
+  </si>
+  <si>
+    <t>t1_25</t>
+  </si>
+  <si>
+    <t>t1_26</t>
+  </si>
+  <si>
+    <t>t1_27</t>
+  </si>
+  <si>
+    <t>t1_28</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
   </numFmts>
   <fonts count="15" x14ac:knownFonts="1">
     <font>
@@ -993,7 +1130,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -1154,61 +1291,9 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -1231,7 +1316,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1245,15 +1330,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1317,14 +1393,33 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1339,6 +1434,24 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1402,7 +1515,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1411,16 +1524,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1437,33 +1552,29 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1471,66 +1582,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1845,427 +1910,425 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="66.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="107"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+    </row>
+    <row r="2" spans="1:11" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="20"/>
+    </row>
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="68" t="str">
+        <f>"Протокол поверки № 10/"&amp;C128&amp;"/"&amp;E6</f>
+        <v>Протокол поверки № 10/_date/_numb</v>
+      </c>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+    </row>
+    <row r="4" spans="1:11" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="20"/>
+    </row>
+    <row r="5" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="65" t="s">
         <v>156</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
-    </row>
-    <row r="2" spans="1:11" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="23"/>
-    </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="56" t="str">
-        <f>"Протокол поверки № 10/"&amp;C150&amp;"/"&amp;E6</f>
-        <v>Протокол поверки № 10//_numb</v>
-      </c>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
-    </row>
-    <row r="4" spans="1:11" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="25"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="23"/>
-    </row>
-    <row r="5" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="53" t="s">
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="36"/>
+    </row>
+    <row r="6" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="65" t="s">
         <v>157</v>
       </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="36" t="s">
-        <v>188</v>
-      </c>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="38" t="s">
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="57" t="s">
         <v>189</v>
       </c>
-      <c r="I5" s="37"/>
-      <c r="J5" s="37"/>
-      <c r="K5" s="39"/>
-    </row>
-    <row r="6" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="53" t="s">
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="57"/>
+    </row>
+    <row r="7" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="65" t="s">
         <v>158</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="45" t="s">
+      <c r="B7" s="65"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="58"/>
+      <c r="K7" s="58"/>
+    </row>
+    <row r="8" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="65" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" s="65"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="58" t="s">
+        <v>175</v>
+      </c>
+      <c r="F8" s="58"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="58"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="58"/>
+      <c r="K8" s="58"/>
+    </row>
+    <row r="9" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="65" t="s">
+        <v>160</v>
+      </c>
+      <c r="B9" s="65"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="58"/>
+      <c r="K9" s="58"/>
+    </row>
+    <row r="10" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="66" t="s">
+        <v>161</v>
+      </c>
+      <c r="B10" s="66"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="59"/>
+      <c r="K10" s="59"/>
+    </row>
+    <row r="11" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="66" t="s">
+        <v>162</v>
+      </c>
+      <c r="B11" s="66"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="67" t="s">
+        <v>163</v>
+      </c>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="67"/>
+      <c r="K11" s="67"/>
+    </row>
+    <row r="12" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="20"/>
+    </row>
+    <row r="13" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="20"/>
+    </row>
+    <row r="14" spans="1:11" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="21"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="20"/>
+    </row>
+    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="46" t="s">
+        <v>165</v>
+      </c>
+      <c r="B15" s="46"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="62" t="s">
+        <v>166</v>
+      </c>
+      <c r="G15" s="62"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="46" t="s">
+        <v>167</v>
+      </c>
+      <c r="J15" s="46"/>
+      <c r="K15" s="46"/>
+    </row>
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="63" t="s">
+        <v>168</v>
+      </c>
+      <c r="B16" s="63"/>
+      <c r="C16" s="63"/>
+      <c r="D16" s="63"/>
+      <c r="E16" s="63"/>
+      <c r="F16" s="64" t="s">
         <v>190</v>
       </c>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-    </row>
-    <row r="7" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="53" t="s">
-        <v>159</v>
-      </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="46"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
-    </row>
-    <row r="8" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A8" s="53" t="s">
-        <v>160</v>
-      </c>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="46" t="s">
-        <v>176</v>
-      </c>
-      <c r="F8" s="46"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="46"/>
-      <c r="J8" s="46"/>
-      <c r="K8" s="46"/>
-    </row>
-    <row r="9" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="53" t="s">
-        <v>161</v>
-      </c>
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="46"/>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
-    </row>
-    <row r="10" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="54" t="s">
-        <v>162</v>
-      </c>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="47" t="s">
+      <c r="G16" s="64"/>
+      <c r="H16" s="64"/>
+      <c r="I16" s="46" t="s">
         <v>177</v>
       </c>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="47"/>
-      <c r="K10" s="47"/>
-    </row>
-    <row r="11" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="54" t="s">
-        <v>163</v>
-      </c>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="55" t="s">
-        <v>164</v>
-      </c>
-      <c r="F11" s="55"/>
-      <c r="G11" s="55"/>
-      <c r="H11" s="55"/>
-      <c r="I11" s="55"/>
-      <c r="J11" s="55"/>
-      <c r="K11" s="55"/>
-    </row>
-    <row r="12" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="24"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="23"/>
-    </row>
-    <row r="13" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
-        <v>165</v>
-      </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="23"/>
-    </row>
-    <row r="14" spans="1:11" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="24"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="23"/>
-    </row>
-    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="40" t="s">
-        <v>166</v>
-      </c>
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="50" t="s">
-        <v>167</v>
-      </c>
-      <c r="G15" s="50"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="40" t="s">
-        <v>168</v>
-      </c>
-      <c r="J15" s="40"/>
-      <c r="K15" s="40"/>
-    </row>
-    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="51" t="s">
+      <c r="J16" s="46"/>
+      <c r="K16" s="46"/>
+    </row>
+    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="63" t="s">
         <v>169</v>
       </c>
-      <c r="B16" s="51"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="52" t="s">
+      <c r="B17" s="63"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="64" t="s">
         <v>191</v>
       </c>
-      <c r="G16" s="52"/>
-      <c r="H16" s="52"/>
-      <c r="I16" s="40" t="s">
+      <c r="G17" s="64"/>
+      <c r="H17" s="64"/>
+      <c r="I17" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="J17" s="46"/>
+      <c r="K17" s="46"/>
+    </row>
+    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="63" t="s">
+        <v>171</v>
+      </c>
+      <c r="B18" s="63"/>
+      <c r="C18" s="63"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="64" t="s">
+        <v>192</v>
+      </c>
+      <c r="G18" s="64"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="46" t="s">
         <v>178</v>
       </c>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-    </row>
-    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="51" t="s">
-        <v>170</v>
-      </c>
-      <c r="B17" s="51"/>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="52" t="s">
-        <v>192</v>
-      </c>
-      <c r="G17" s="52"/>
-      <c r="H17" s="52"/>
-      <c r="I17" s="40" t="s">
-        <v>171</v>
-      </c>
-      <c r="J17" s="40"/>
-      <c r="K17" s="40"/>
-    </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="51" t="s">
+      <c r="J18" s="46"/>
+      <c r="K18" s="46"/>
+    </row>
+    <row r="19" spans="1:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="24"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="20"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" s="29" t="s">
         <v>172</v>
       </c>
-      <c r="B18" s="51"/>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="52" t="s">
-        <v>193</v>
-      </c>
-      <c r="G18" s="52"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="40" t="s">
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="21"/>
+    </row>
+    <row r="21" spans="1:11" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="29"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="21"/>
+    </row>
+    <row r="22" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="62" t="s">
+        <v>173</v>
+      </c>
+      <c r="B22" s="62"/>
+      <c r="C22" s="62" t="s">
+        <v>174</v>
+      </c>
+      <c r="D22" s="62"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="21"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23" s="50" t="s">
         <v>179</v>
       </c>
-      <c r="J18" s="40"/>
-      <c r="K18" s="40"/>
-    </row>
-    <row r="19" spans="1:11" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="27"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="23"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="32" t="s">
-        <v>173</v>
-      </c>
-      <c r="B20" s="32"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="24"/>
-    </row>
-    <row r="21" spans="1:11" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="32"/>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="24"/>
-    </row>
-    <row r="22" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="B22" s="50"/>
-      <c r="C22" s="50" t="s">
-        <v>175</v>
-      </c>
-      <c r="D22" s="50"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="24"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="44" t="s">
-        <v>180</v>
-      </c>
-      <c r="B23" s="44"/>
-      <c r="C23" s="48">
+      <c r="B23" s="50"/>
+      <c r="C23" s="60">
         <v>276568182</v>
       </c>
-      <c r="D23" s="49"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="34"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
     </row>
     <row r="24" spans="1:11" ht="74.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="22"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
     </row>
     <row r="25" spans="1:11" ht="74.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="22"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="22"/>
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
     </row>
     <row r="26" spans="1:11" ht="74.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="22"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
     </row>
     <row r="27" spans="1:11" ht="74.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="22"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="22"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
     </row>
     <row r="28" spans="1:11" ht="74.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="22"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="22"/>
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
     </row>
     <row r="29" spans="1:11" ht="74.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="22"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="22"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="22"/>
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
     </row>
     <row r="30" spans="1:11" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="14"/>
+      <c r="A30" s="11"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -2278,14 +2341,14 @@
       <c r="K30" s="2"/>
     </row>
     <row r="31" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
+      <c r="A31" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="B31" s="10"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -2293,12 +2356,12 @@
       <c r="K31" s="2"/>
     </row>
     <row r="32" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="13"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
@@ -2306,14 +2369,14 @@
       <c r="K32" s="2"/>
     </row>
     <row r="33" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
+      <c r="A33" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
@@ -2334,19 +2397,19 @@
       <c r="K34" s="2"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A35" s="84" t="s">
-        <v>181</v>
-      </c>
-      <c r="B35" s="84"/>
-      <c r="C35" s="84"/>
-      <c r="D35" s="84"/>
-      <c r="E35" s="84"/>
-      <c r="F35" s="84"/>
-      <c r="G35" s="84"/>
-      <c r="H35" s="84"/>
-      <c r="I35" s="84"/>
-      <c r="J35" s="84"/>
-      <c r="K35" s="84"/>
+      <c r="A35" s="97" t="s">
+        <v>180</v>
+      </c>
+      <c r="B35" s="97"/>
+      <c r="C35" s="97"/>
+      <c r="D35" s="97"/>
+      <c r="E35" s="97"/>
+      <c r="F35" s="97"/>
+      <c r="G35" s="97"/>
+      <c r="H35" s="97"/>
+      <c r="I35" s="97"/>
+      <c r="J35" s="97"/>
+      <c r="K35" s="97"/>
     </row>
     <row r="36" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
@@ -2363,7 +2426,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -2377,255 +2440,299 @@
       <c r="K37" s="2"/>
     </row>
     <row r="38" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="41" t="s">
+      <c r="A38" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B38" s="42"/>
-      <c r="C38" s="74" t="s">
+      <c r="B38" s="48"/>
+      <c r="C38" s="88" t="s">
         <v>151</v>
       </c>
-      <c r="D38" s="75"/>
-      <c r="E38" s="74" t="s">
+      <c r="D38" s="89"/>
+      <c r="E38" s="88" t="s">
         <v>152</v>
       </c>
-      <c r="F38" s="75"/>
-      <c r="G38" s="74" t="s">
+      <c r="F38" s="89"/>
+      <c r="G38" s="88" t="s">
         <v>153</v>
       </c>
-      <c r="H38" s="75"/>
-      <c r="I38" s="74" t="s">
+      <c r="H38" s="89"/>
+      <c r="I38" s="88" t="s">
         <v>154</v>
       </c>
-      <c r="J38" s="75"/>
-      <c r="K38" s="41" t="s">
+      <c r="J38" s="89"/>
+      <c r="K38" s="47" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A39" s="42"/>
-      <c r="B39" s="42"/>
-      <c r="C39" s="76"/>
-      <c r="D39" s="77"/>
-      <c r="E39" s="76"/>
-      <c r="F39" s="77"/>
-      <c r="G39" s="76"/>
-      <c r="H39" s="77"/>
-      <c r="I39" s="76"/>
-      <c r="J39" s="77"/>
-      <c r="K39" s="42"/>
+      <c r="A39" s="48"/>
+      <c r="B39" s="48"/>
+      <c r="C39" s="90"/>
+      <c r="D39" s="91"/>
+      <c r="E39" s="90"/>
+      <c r="F39" s="91"/>
+      <c r="G39" s="90"/>
+      <c r="H39" s="91"/>
+      <c r="I39" s="90"/>
+      <c r="J39" s="91"/>
+      <c r="K39" s="48"/>
     </row>
     <row r="40" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A40" s="41" t="s">
+      <c r="A40" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="B40" s="42"/>
-      <c r="C40" s="92" t="s">
-        <v>194</v>
-      </c>
-      <c r="D40" s="93"/>
-      <c r="E40" s="92" t="s">
-        <v>205</v>
-      </c>
-      <c r="F40" s="93"/>
-      <c r="G40" s="82"/>
-      <c r="H40" s="83"/>
-      <c r="I40" s="82"/>
-      <c r="J40" s="83"/>
-      <c r="K40" s="78">
+      <c r="B40" s="48"/>
+      <c r="C40" s="95" t="s">
+        <v>228</v>
+      </c>
+      <c r="D40" s="96"/>
+      <c r="E40" s="95" t="s">
+        <v>239</v>
+      </c>
+      <c r="F40" s="96"/>
+      <c r="G40" s="95" t="s">
+        <v>240</v>
+      </c>
+      <c r="H40" s="96"/>
+      <c r="I40" s="95" t="s">
+        <v>241</v>
+      </c>
+      <c r="J40" s="96"/>
+      <c r="K40" s="92">
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="14.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="88" t="s">
+    <row r="41" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A41" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="B41" s="72"/>
-      <c r="C41" s="94" t="s">
-        <v>195</v>
-      </c>
-      <c r="D41" s="95"/>
-      <c r="E41" s="94" t="s">
-        <v>206</v>
-      </c>
-      <c r="F41" s="95"/>
-      <c r="G41" s="85"/>
-      <c r="H41" s="86"/>
-      <c r="I41" s="85"/>
-      <c r="J41" s="86"/>
-      <c r="K41" s="79"/>
+      <c r="B41" s="48"/>
+      <c r="C41" s="95" t="s">
+        <v>229</v>
+      </c>
+      <c r="D41" s="96"/>
+      <c r="E41" s="95" t="s">
+        <v>242</v>
+      </c>
+      <c r="F41" s="96"/>
+      <c r="G41" s="95" t="s">
+        <v>243</v>
+      </c>
+      <c r="H41" s="96"/>
+      <c r="I41" s="95" t="s">
+        <v>244</v>
+      </c>
+      <c r="J41" s="96"/>
+      <c r="K41" s="92"/>
     </row>
     <row r="42" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A42" s="62" t="s">
+      <c r="A42" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="B42" s="87"/>
-      <c r="C42" s="96" t="s">
-        <v>196</v>
-      </c>
-      <c r="D42" s="97"/>
-      <c r="E42" s="96" t="s">
-        <v>207</v>
-      </c>
-      <c r="F42" s="97"/>
-      <c r="G42" s="76"/>
-      <c r="H42" s="77"/>
-      <c r="I42" s="76"/>
-      <c r="J42" s="77"/>
-      <c r="K42" s="80">
+      <c r="B42" s="86"/>
+      <c r="C42" s="98" t="s">
+        <v>230</v>
+      </c>
+      <c r="D42" s="99"/>
+      <c r="E42" s="95" t="s">
+        <v>245</v>
+      </c>
+      <c r="F42" s="96"/>
+      <c r="G42" s="95" t="s">
+        <v>246</v>
+      </c>
+      <c r="H42" s="96"/>
+      <c r="I42" s="95" t="s">
+        <v>247</v>
+      </c>
+      <c r="J42" s="96"/>
+      <c r="K42" s="93">
         <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A43" s="41" t="s">
+      <c r="A43" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="B43" s="42"/>
-      <c r="C43" s="92" t="s">
-        <v>197</v>
-      </c>
-      <c r="D43" s="93"/>
-      <c r="E43" s="92" t="s">
-        <v>208</v>
-      </c>
-      <c r="F43" s="93"/>
-      <c r="G43" s="82"/>
-      <c r="H43" s="83"/>
-      <c r="I43" s="82"/>
-      <c r="J43" s="83"/>
-      <c r="K43" s="80"/>
+      <c r="B43" s="48"/>
+      <c r="C43" s="95" t="s">
+        <v>231</v>
+      </c>
+      <c r="D43" s="96"/>
+      <c r="E43" s="95" t="s">
+        <v>248</v>
+      </c>
+      <c r="F43" s="96"/>
+      <c r="G43" s="95" t="s">
+        <v>249</v>
+      </c>
+      <c r="H43" s="96"/>
+      <c r="I43" s="95" t="s">
+        <v>250</v>
+      </c>
+      <c r="J43" s="96"/>
+      <c r="K43" s="93"/>
     </row>
     <row r="44" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A44" s="41" t="s">
+      <c r="A44" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="B44" s="42"/>
-      <c r="C44" s="92" t="s">
-        <v>198</v>
-      </c>
-      <c r="D44" s="93"/>
-      <c r="E44" s="92" t="s">
-        <v>209</v>
-      </c>
-      <c r="F44" s="93"/>
-      <c r="G44" s="82"/>
-      <c r="H44" s="83"/>
-      <c r="I44" s="82"/>
-      <c r="J44" s="83"/>
-      <c r="K44" s="80"/>
+      <c r="B44" s="48"/>
+      <c r="C44" s="95" t="s">
+        <v>232</v>
+      </c>
+      <c r="D44" s="96"/>
+      <c r="E44" s="95" t="s">
+        <v>251</v>
+      </c>
+      <c r="F44" s="96"/>
+      <c r="G44" s="95" t="s">
+        <v>252</v>
+      </c>
+      <c r="H44" s="96"/>
+      <c r="I44" s="95" t="s">
+        <v>253</v>
+      </c>
+      <c r="J44" s="96"/>
+      <c r="K44" s="93"/>
     </row>
     <row r="45" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A45" s="41" t="s">
+      <c r="A45" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="B45" s="42"/>
-      <c r="C45" s="92" t="s">
-        <v>199</v>
-      </c>
-      <c r="D45" s="93"/>
-      <c r="E45" s="92" t="s">
-        <v>210</v>
-      </c>
-      <c r="F45" s="93"/>
-      <c r="G45" s="82"/>
-      <c r="H45" s="83"/>
-      <c r="I45" s="82"/>
-      <c r="J45" s="83"/>
-      <c r="K45" s="80"/>
+      <c r="B45" s="48"/>
+      <c r="C45" s="95" t="s">
+        <v>233</v>
+      </c>
+      <c r="D45" s="96"/>
+      <c r="E45" s="95" t="s">
+        <v>254</v>
+      </c>
+      <c r="F45" s="96"/>
+      <c r="G45" s="95" t="s">
+        <v>255</v>
+      </c>
+      <c r="H45" s="96"/>
+      <c r="I45" s="95" t="s">
+        <v>256</v>
+      </c>
+      <c r="J45" s="96"/>
+      <c r="K45" s="93"/>
     </row>
     <row r="46" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A46" s="41" t="s">
+      <c r="A46" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="B46" s="42"/>
-      <c r="C46" s="92" t="s">
-        <v>200</v>
-      </c>
-      <c r="D46" s="93"/>
-      <c r="E46" s="92" t="s">
-        <v>211</v>
-      </c>
-      <c r="F46" s="93"/>
-      <c r="G46" s="82"/>
-      <c r="H46" s="83"/>
-      <c r="I46" s="82"/>
-      <c r="J46" s="83"/>
-      <c r="K46" s="80"/>
+      <c r="B46" s="48"/>
+      <c r="C46" s="95" t="s">
+        <v>234</v>
+      </c>
+      <c r="D46" s="96"/>
+      <c r="E46" s="95" t="s">
+        <v>257</v>
+      </c>
+      <c r="F46" s="96"/>
+      <c r="G46" s="95" t="s">
+        <v>258</v>
+      </c>
+      <c r="H46" s="96"/>
+      <c r="I46" s="95" t="s">
+        <v>259</v>
+      </c>
+      <c r="J46" s="96"/>
+      <c r="K46" s="93"/>
     </row>
     <row r="47" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A47" s="41" t="s">
+      <c r="A47" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="B47" s="42"/>
-      <c r="C47" s="92" t="s">
-        <v>201</v>
-      </c>
-      <c r="D47" s="93"/>
-      <c r="E47" s="92" t="s">
-        <v>212</v>
-      </c>
-      <c r="F47" s="93"/>
-      <c r="G47" s="82"/>
-      <c r="H47" s="83"/>
-      <c r="I47" s="82"/>
-      <c r="J47" s="83"/>
-      <c r="K47" s="80"/>
+      <c r="B47" s="48"/>
+      <c r="C47" s="95" t="s">
+        <v>235</v>
+      </c>
+      <c r="D47" s="96"/>
+      <c r="E47" s="95" t="s">
+        <v>260</v>
+      </c>
+      <c r="F47" s="96"/>
+      <c r="G47" s="95" t="s">
+        <v>261</v>
+      </c>
+      <c r="H47" s="96"/>
+      <c r="I47" s="95" t="s">
+        <v>262</v>
+      </c>
+      <c r="J47" s="96"/>
+      <c r="K47" s="93"/>
     </row>
     <row r="48" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A48" s="41" t="s">
+      <c r="A48" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="B48" s="42"/>
-      <c r="C48" s="92" t="s">
-        <v>202</v>
-      </c>
-      <c r="D48" s="93"/>
-      <c r="E48" s="92" t="s">
-        <v>213</v>
-      </c>
-      <c r="F48" s="93"/>
-      <c r="G48" s="82"/>
-      <c r="H48" s="83"/>
-      <c r="I48" s="82"/>
-      <c r="J48" s="83"/>
-      <c r="K48" s="80"/>
+      <c r="B48" s="48"/>
+      <c r="C48" s="95" t="s">
+        <v>236</v>
+      </c>
+      <c r="D48" s="96"/>
+      <c r="E48" s="95" t="s">
+        <v>263</v>
+      </c>
+      <c r="F48" s="96"/>
+      <c r="G48" s="95" t="s">
+        <v>264</v>
+      </c>
+      <c r="H48" s="96"/>
+      <c r="I48" s="95" t="s">
+        <v>265</v>
+      </c>
+      <c r="J48" s="96"/>
+      <c r="K48" s="93"/>
     </row>
     <row r="49" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="43" t="s">
+      <c r="A49" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="B49" s="42"/>
-      <c r="C49" s="92" t="s">
-        <v>203</v>
-      </c>
-      <c r="D49" s="93"/>
-      <c r="E49" s="92" t="s">
-        <v>214</v>
-      </c>
-      <c r="F49" s="93"/>
-      <c r="G49" s="82"/>
-      <c r="H49" s="83"/>
-      <c r="I49" s="82"/>
-      <c r="J49" s="83"/>
-      <c r="K49" s="80"/>
+      <c r="B49" s="48"/>
+      <c r="C49" s="95" t="s">
+        <v>237</v>
+      </c>
+      <c r="D49" s="96"/>
+      <c r="E49" s="95" t="s">
+        <v>266</v>
+      </c>
+      <c r="F49" s="96"/>
+      <c r="G49" s="95" t="s">
+        <v>267</v>
+      </c>
+      <c r="H49" s="96"/>
+      <c r="I49" s="95" t="s">
+        <v>268</v>
+      </c>
+      <c r="J49" s="96"/>
+      <c r="K49" s="93"/>
     </row>
     <row r="50" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="43" t="s">
+      <c r="A50" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="B50" s="42"/>
-      <c r="C50" s="92" t="s">
-        <v>204</v>
-      </c>
-      <c r="D50" s="93"/>
-      <c r="E50" s="92" t="s">
-        <v>215</v>
-      </c>
-      <c r="F50" s="93"/>
-      <c r="G50" s="82"/>
-      <c r="H50" s="83"/>
-      <c r="I50" s="82"/>
-      <c r="J50" s="83"/>
-      <c r="K50" s="81"/>
+      <c r="B50" s="48"/>
+      <c r="C50" s="95" t="s">
+        <v>238</v>
+      </c>
+      <c r="D50" s="96"/>
+      <c r="E50" s="95" t="s">
+        <v>269</v>
+      </c>
+      <c r="F50" s="96"/>
+      <c r="G50" s="95" t="s">
+        <v>270</v>
+      </c>
+      <c r="H50" s="96"/>
+      <c r="I50" s="95" t="s">
+        <v>271</v>
+      </c>
+      <c r="J50" s="96"/>
+      <c r="K50" s="94"/>
     </row>
     <row r="51" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="5"/>
@@ -2642,7 +2749,7 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -2657,55 +2764,58 @@
     </row>
     <row r="53" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="B53" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="B53" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C53" s="42"/>
+      <c r="C53" s="48"/>
       <c r="D53" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E53" s="41" t="s">
+      <c r="E53" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="F53" s="41"/>
-      <c r="G53" s="43" t="s">
+      <c r="F53" s="47"/>
+      <c r="G53" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="H53" s="43"/>
-      <c r="I53" s="43" t="s">
+      <c r="H53" s="49"/>
+      <c r="I53" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="J53" s="43"/>
+      <c r="J53" s="49"/>
       <c r="K53" s="6"/>
-      <c r="M53" s="17"/>
-      <c r="N53" s="17"/>
-      <c r="O53" s="17"/>
-      <c r="P53" s="17"/>
-      <c r="Q53" s="17"/>
+      <c r="M53" s="14"/>
+      <c r="N53" s="14"/>
+      <c r="O53" s="14"/>
+      <c r="P53" s="14"/>
+      <c r="Q53" s="14"/>
     </row>
     <row r="54" spans="1:17" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="60" t="s">
+      <c r="A54" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="B54" s="62" t="s">
+      <c r="B54" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="C54" s="87"/>
-      <c r="D54" s="16" t="s">
+      <c r="C54" s="86"/>
+      <c r="D54" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="E54" s="98" t="s">
-        <v>194</v>
-      </c>
-      <c r="F54" s="98"/>
-      <c r="G54" s="71"/>
-      <c r="H54" s="71"/>
-      <c r="I54" s="71" t="s">
+      <c r="E54" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="F54" s="51"/>
+      <c r="G54" s="84" t="e">
+        <f>E54-0.006</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H54" s="84"/>
+      <c r="I54" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="J54" s="71"/>
+      <c r="J54" s="52"/>
       <c r="K54" s="6"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5"/>
@@ -2714,24 +2824,27 @@
       <c r="Q54" s="5"/>
     </row>
     <row r="55" spans="1:17" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="43"/>
-      <c r="B55" s="41" t="s">
+      <c r="A55" s="49"/>
+      <c r="B55" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="C55" s="42"/>
-      <c r="D55" s="12" t="s">
+      <c r="C55" s="48"/>
+      <c r="D55" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E55" s="98" t="s">
-        <v>195</v>
-      </c>
-      <c r="F55" s="98"/>
-      <c r="G55" s="66"/>
-      <c r="H55" s="66"/>
-      <c r="I55" s="66" t="s">
+      <c r="E55" s="51" t="s">
+        <v>194</v>
+      </c>
+      <c r="F55" s="51"/>
+      <c r="G55" s="84" t="e">
+        <f>E55-0.03</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H55" s="84"/>
+      <c r="I55" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="J55" s="66"/>
+      <c r="J55" s="53"/>
       <c r="K55" s="6"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
@@ -2740,24 +2853,27 @@
       <c r="Q55" s="5"/>
     </row>
     <row r="56" spans="1:17" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A56" s="43"/>
-      <c r="B56" s="41" t="s">
+      <c r="A56" s="49"/>
+      <c r="B56" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="C56" s="42"/>
-      <c r="D56" s="12" t="s">
+      <c r="C56" s="48"/>
+      <c r="D56" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E56" s="98" t="s">
-        <v>196</v>
-      </c>
-      <c r="F56" s="98"/>
-      <c r="G56" s="66"/>
-      <c r="H56" s="66"/>
-      <c r="I56" s="66" t="s">
+      <c r="E56" s="51" t="s">
+        <v>195</v>
+      </c>
+      <c r="F56" s="51"/>
+      <c r="G56" s="84" t="e">
+        <f>E56-0.3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H56" s="84"/>
+      <c r="I56" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="J56" s="66"/>
+      <c r="J56" s="53"/>
       <c r="K56" s="6"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5"/>
@@ -2766,24 +2882,27 @@
       <c r="Q56" s="5"/>
     </row>
     <row r="57" spans="1:17" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="43"/>
-      <c r="B57" s="41" t="s">
+      <c r="A57" s="49"/>
+      <c r="B57" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="C57" s="42"/>
-      <c r="D57" s="12" t="s">
+      <c r="C57" s="48"/>
+      <c r="D57" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E57" s="98" t="s">
-        <v>197</v>
-      </c>
-      <c r="F57" s="98"/>
-      <c r="G57" s="66"/>
-      <c r="H57" s="66"/>
-      <c r="I57" s="66" t="s">
+      <c r="E57" s="51" t="s">
+        <v>196</v>
+      </c>
+      <c r="F57" s="51"/>
+      <c r="G57" s="84" t="e">
+        <f>E57-3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H57" s="84"/>
+      <c r="I57" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="J57" s="66"/>
+      <c r="J57" s="53"/>
       <c r="K57" s="6"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5"/>
@@ -2792,24 +2911,27 @@
       <c r="Q57" s="5"/>
     </row>
     <row r="58" spans="1:17" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="63"/>
-      <c r="B58" s="63" t="s">
+      <c r="A58" s="75"/>
+      <c r="B58" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="C58" s="72"/>
-      <c r="D58" s="19" t="s">
+      <c r="C58" s="85"/>
+      <c r="D58" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="E58" s="99" t="s">
-        <v>198</v>
-      </c>
-      <c r="F58" s="99"/>
-      <c r="G58" s="69"/>
-      <c r="H58" s="69"/>
-      <c r="I58" s="69" t="s">
+      <c r="E58" s="54" t="s">
+        <v>197</v>
+      </c>
+      <c r="F58" s="54"/>
+      <c r="G58" s="56" t="e">
+        <f>E58-15</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H58" s="56"/>
+      <c r="I58" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="J58" s="69"/>
+      <c r="J58" s="55"/>
       <c r="K58" s="6"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5"/>
@@ -2818,26 +2940,29 @@
       <c r="Q58" s="5"/>
     </row>
     <row r="59" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="64" t="s">
+      <c r="A59" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="B59" s="65" t="s">
+      <c r="B59" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="C59" s="73"/>
-      <c r="D59" s="18" t="s">
+      <c r="C59" s="87"/>
+      <c r="D59" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="E59" s="98" t="s">
-        <v>205</v>
-      </c>
-      <c r="F59" s="98"/>
-      <c r="G59" s="70"/>
-      <c r="H59" s="70"/>
-      <c r="I59" s="70" t="s">
+      <c r="E59" s="51" t="s">
+        <v>198</v>
+      </c>
+      <c r="F59" s="51"/>
+      <c r="G59" s="84" t="e">
+        <f>E59-0.006</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H59" s="84"/>
+      <c r="I59" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="J59" s="70"/>
+      <c r="J59" s="83"/>
       <c r="K59" s="6"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
@@ -2846,24 +2971,27 @@
       <c r="Q59" s="5"/>
     </row>
     <row r="60" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="43"/>
-      <c r="B60" s="41" t="s">
+      <c r="A60" s="49"/>
+      <c r="B60" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="C60" s="42"/>
-      <c r="D60" s="12" t="s">
+      <c r="C60" s="48"/>
+      <c r="D60" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E60" s="98" t="s">
-        <v>206</v>
-      </c>
-      <c r="F60" s="98"/>
-      <c r="G60" s="66"/>
-      <c r="H60" s="66"/>
-      <c r="I60" s="66" t="s">
+      <c r="E60" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="F60" s="51"/>
+      <c r="G60" s="84" t="e">
+        <f>E60-0.03</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H60" s="84"/>
+      <c r="I60" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="J60" s="66"/>
+      <c r="J60" s="53"/>
       <c r="K60" s="6"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
@@ -2872,24 +3000,27 @@
       <c r="Q60" s="5"/>
     </row>
     <row r="61" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="43"/>
-      <c r="B61" s="41" t="s">
+      <c r="A61" s="49"/>
+      <c r="B61" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="C61" s="42"/>
-      <c r="D61" s="12" t="s">
+      <c r="C61" s="48"/>
+      <c r="D61" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E61" s="98" t="s">
-        <v>207</v>
-      </c>
-      <c r="F61" s="98"/>
-      <c r="G61" s="66"/>
-      <c r="H61" s="66"/>
-      <c r="I61" s="66" t="s">
+      <c r="E61" s="51" t="s">
+        <v>200</v>
+      </c>
+      <c r="F61" s="51"/>
+      <c r="G61" s="84" t="e">
+        <f>E61-0.3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H61" s="84"/>
+      <c r="I61" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="J61" s="66"/>
+      <c r="J61" s="53"/>
       <c r="K61" s="6"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
@@ -2898,24 +3029,27 @@
       <c r="Q61" s="5"/>
     </row>
     <row r="62" spans="1:17" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A62" s="43"/>
-      <c r="B62" s="41" t="s">
+      <c r="A62" s="49"/>
+      <c r="B62" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="C62" s="42"/>
-      <c r="D62" s="12" t="s">
+      <c r="C62" s="48"/>
+      <c r="D62" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E62" s="98" t="s">
-        <v>208</v>
-      </c>
-      <c r="F62" s="98"/>
-      <c r="G62" s="66"/>
-      <c r="H62" s="66"/>
-      <c r="I62" s="66" t="s">
+      <c r="E62" s="51" t="s">
+        <v>201</v>
+      </c>
+      <c r="F62" s="51"/>
+      <c r="G62" s="84" t="e">
+        <f>E62-3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H62" s="84"/>
+      <c r="I62" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="J62" s="66"/>
+      <c r="J62" s="53"/>
       <c r="K62" s="6"/>
       <c r="M62" s="5"/>
       <c r="N62" s="5"/>
@@ -2924,24 +3058,27 @@
       <c r="Q62" s="5"/>
     </row>
     <row r="63" spans="1:17" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="63"/>
-      <c r="B63" s="63" t="s">
+      <c r="A63" s="75"/>
+      <c r="B63" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="C63" s="72"/>
-      <c r="D63" s="19" t="s">
+      <c r="C63" s="85"/>
+      <c r="D63" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="E63" s="98" t="s">
-        <v>209</v>
-      </c>
-      <c r="F63" s="98"/>
-      <c r="G63" s="69"/>
-      <c r="H63" s="69"/>
-      <c r="I63" s="69" t="s">
+      <c r="E63" s="54" t="s">
+        <v>202</v>
+      </c>
+      <c r="F63" s="54"/>
+      <c r="G63" s="56" t="e">
+        <f>E63-15</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H63" s="56"/>
+      <c r="I63" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="J63" s="69"/>
+      <c r="J63" s="55"/>
       <c r="K63" s="6"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
@@ -2949,25 +3086,30 @@
       <c r="P63" s="5"/>
       <c r="Q63" s="5"/>
     </row>
-    <row r="64" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="64" t="s">
+    <row r="64" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="B64" s="65" t="s">
+      <c r="B64" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="C64" s="73"/>
-      <c r="D64" s="18" t="s">
+      <c r="C64" s="87"/>
+      <c r="D64" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="E64" s="70"/>
-      <c r="F64" s="70"/>
-      <c r="G64" s="70"/>
-      <c r="H64" s="70"/>
-      <c r="I64" s="70" t="s">
+      <c r="E64" s="51" t="s">
+        <v>218</v>
+      </c>
+      <c r="F64" s="51"/>
+      <c r="G64" s="52" t="e">
+        <f>E64-6</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H64" s="52"/>
+      <c r="I64" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="J64" s="70"/>
+      <c r="J64" s="83"/>
       <c r="K64" s="6"/>
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
@@ -2975,23 +3117,28 @@
       <c r="P64" s="5"/>
       <c r="Q64" s="5"/>
     </row>
-    <row r="65" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="43"/>
-      <c r="B65" s="41" t="s">
+    <row r="65" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="49"/>
+      <c r="B65" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="C65" s="42"/>
-      <c r="D65" s="12" t="s">
+      <c r="C65" s="48"/>
+      <c r="D65" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E65" s="66"/>
-      <c r="F65" s="66"/>
-      <c r="G65" s="66"/>
-      <c r="H65" s="66"/>
-      <c r="I65" s="66" t="s">
+      <c r="E65" s="51" t="s">
+        <v>219</v>
+      </c>
+      <c r="F65" s="51"/>
+      <c r="G65" s="52" t="e">
+        <f>E65-30</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H65" s="52"/>
+      <c r="I65" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="J65" s="66"/>
+      <c r="J65" s="53"/>
       <c r="K65" s="6"/>
       <c r="M65" s="5"/>
       <c r="N65" s="5"/>
@@ -2999,23 +3146,28 @@
       <c r="P65" s="5"/>
       <c r="Q65" s="5"/>
     </row>
-    <row r="66" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="43"/>
-      <c r="B66" s="41" t="s">
+    <row r="66" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="49"/>
+      <c r="B66" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="C66" s="42"/>
-      <c r="D66" s="12" t="s">
+      <c r="C66" s="48"/>
+      <c r="D66" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E66" s="66"/>
-      <c r="F66" s="66"/>
-      <c r="G66" s="66"/>
-      <c r="H66" s="66"/>
-      <c r="I66" s="66" t="s">
+      <c r="E66" s="51" t="s">
+        <v>272</v>
+      </c>
+      <c r="F66" s="51"/>
+      <c r="G66" s="52" t="e">
+        <f>E66-300</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H66" s="52"/>
+      <c r="I66" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="J66" s="66"/>
+      <c r="J66" s="53"/>
       <c r="K66" s="6"/>
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
@@ -3023,23 +3175,28 @@
       <c r="P66" s="5"/>
       <c r="Q66" s="5"/>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A67" s="43"/>
-      <c r="B67" s="41" t="s">
+    <row r="67" spans="1:17" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A67" s="49"/>
+      <c r="B67" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="C67" s="42"/>
-      <c r="D67" s="12" t="s">
+      <c r="C67" s="48"/>
+      <c r="D67" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E67" s="66"/>
-      <c r="F67" s="66"/>
-      <c r="G67" s="66"/>
-      <c r="H67" s="66"/>
-      <c r="I67" s="66" t="s">
+      <c r="E67" s="51" t="s">
+        <v>273</v>
+      </c>
+      <c r="F67" s="51"/>
+      <c r="G67" s="52" t="e">
+        <f>E67-3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H67" s="52"/>
+      <c r="I67" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="J67" s="66"/>
+      <c r="J67" s="53"/>
       <c r="K67" s="6"/>
       <c r="M67" s="5"/>
       <c r="N67" s="5"/>
@@ -3047,23 +3204,28 @@
       <c r="P67" s="5"/>
       <c r="Q67" s="5"/>
     </row>
-    <row r="68" spans="1:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="63"/>
-      <c r="B68" s="63" t="s">
+    <row r="68" spans="1:17" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="75"/>
+      <c r="B68" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="C68" s="72"/>
-      <c r="D68" s="19" t="s">
+      <c r="C68" s="85"/>
+      <c r="D68" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="E68" s="69"/>
-      <c r="F68" s="69"/>
-      <c r="G68" s="69"/>
-      <c r="H68" s="69"/>
-      <c r="I68" s="69" t="s">
+      <c r="E68" s="54" t="s">
+        <v>274</v>
+      </c>
+      <c r="F68" s="54"/>
+      <c r="G68" s="55" t="e">
+        <f>E68-15</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H68" s="55"/>
+      <c r="I68" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="J68" s="69"/>
+      <c r="J68" s="55"/>
       <c r="K68" s="6"/>
       <c r="M68" s="5"/>
       <c r="N68" s="5"/>
@@ -3075,13 +3237,13 @@
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="6"/>
-      <c r="D69" s="35"/>
-      <c r="E69" s="35"/>
-      <c r="F69" s="35"/>
-      <c r="G69" s="35"/>
-      <c r="H69" s="35"/>
-      <c r="I69" s="35"/>
-      <c r="J69" s="35"/>
+      <c r="D69" s="32"/>
+      <c r="E69" s="32"/>
+      <c r="F69" s="32"/>
+      <c r="G69" s="32"/>
+      <c r="H69" s="32"/>
+      <c r="I69" s="32"/>
+      <c r="J69" s="32"/>
       <c r="K69" s="6"/>
       <c r="M69" s="5"/>
       <c r="N69" s="5"/>
@@ -3091,53 +3253,58 @@
     </row>
     <row r="70" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="B70" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="B70" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C70" s="42"/>
+      <c r="C70" s="48"/>
       <c r="D70" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E70" s="41" t="s">
+      <c r="E70" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="F70" s="41"/>
-      <c r="G70" s="43" t="s">
+      <c r="F70" s="47"/>
+      <c r="G70" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="H70" s="43"/>
-      <c r="I70" s="43" t="s">
+      <c r="H70" s="49"/>
+      <c r="I70" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="J70" s="43"/>
+      <c r="J70" s="49"/>
       <c r="K70" s="6"/>
-      <c r="M70" s="17"/>
-      <c r="N70" s="17"/>
-      <c r="O70" s="17"/>
-      <c r="P70" s="17"/>
-      <c r="Q70" s="17"/>
-    </row>
-    <row r="71" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="43" t="s">
+      <c r="M70" s="14"/>
+      <c r="N70" s="14"/>
+      <c r="O70" s="14"/>
+      <c r="P70" s="14"/>
+      <c r="Q70" s="14"/>
+    </row>
+    <row r="71" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="B71" s="41" t="s">
+      <c r="B71" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="C71" s="42"/>
-      <c r="D71" s="12" t="s">
+      <c r="C71" s="48"/>
+      <c r="D71" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E71" s="66"/>
-      <c r="F71" s="66"/>
-      <c r="G71" s="66"/>
-      <c r="H71" s="66"/>
-      <c r="I71" s="66" t="s">
+      <c r="E71" s="51" t="s">
+        <v>220</v>
+      </c>
+      <c r="F71" s="51"/>
+      <c r="G71" s="52" t="e">
+        <f>E71-6</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H71" s="52"/>
+      <c r="I71" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="J71" s="66"/>
+      <c r="J71" s="53"/>
       <c r="K71" s="6"/>
       <c r="M71" s="5"/>
       <c r="N71" s="5"/>
@@ -3145,23 +3312,28 @@
       <c r="P71" s="5"/>
       <c r="Q71" s="5"/>
     </row>
-    <row r="72" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="43"/>
-      <c r="B72" s="41" t="s">
+    <row r="72" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="49"/>
+      <c r="B72" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="C72" s="42"/>
-      <c r="D72" s="12" t="s">
+      <c r="C72" s="48"/>
+      <c r="D72" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E72" s="66"/>
-      <c r="F72" s="66"/>
-      <c r="G72" s="66"/>
-      <c r="H72" s="66"/>
-      <c r="I72" s="66" t="s">
+      <c r="E72" s="51" t="s">
+        <v>221</v>
+      </c>
+      <c r="F72" s="51"/>
+      <c r="G72" s="52" t="e">
+        <f>E72-30</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H72" s="52"/>
+      <c r="I72" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="J72" s="66"/>
+      <c r="J72" s="53"/>
       <c r="K72" s="6"/>
       <c r="M72" s="5"/>
       <c r="N72" s="5"/>
@@ -3169,23 +3341,28 @@
       <c r="P72" s="5"/>
       <c r="Q72" s="5"/>
     </row>
-    <row r="73" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="43"/>
-      <c r="B73" s="41" t="s">
+    <row r="73" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="49"/>
+      <c r="B73" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="C73" s="42"/>
-      <c r="D73" s="12" t="s">
+      <c r="C73" s="48"/>
+      <c r="D73" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E73" s="66"/>
-      <c r="F73" s="66"/>
-      <c r="G73" s="66"/>
-      <c r="H73" s="66"/>
-      <c r="I73" s="66" t="s">
+      <c r="E73" s="51" t="s">
+        <v>275</v>
+      </c>
+      <c r="F73" s="51"/>
+      <c r="G73" s="52" t="e">
+        <f>E73-300</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H73" s="52"/>
+      <c r="I73" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="J73" s="66"/>
+      <c r="J73" s="53"/>
       <c r="K73" s="6"/>
       <c r="M73" s="5"/>
       <c r="N73" s="5"/>
@@ -3193,23 +3370,28 @@
       <c r="P73" s="5"/>
       <c r="Q73" s="5"/>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A74" s="43"/>
-      <c r="B74" s="41" t="s">
+    <row r="74" spans="1:17" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A74" s="49"/>
+      <c r="B74" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="C74" s="42"/>
-      <c r="D74" s="12" t="s">
+      <c r="C74" s="48"/>
+      <c r="D74" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E74" s="66"/>
-      <c r="F74" s="66"/>
-      <c r="G74" s="66"/>
-      <c r="H74" s="66"/>
-      <c r="I74" s="66" t="s">
+      <c r="E74" s="51" t="s">
+        <v>276</v>
+      </c>
+      <c r="F74" s="51"/>
+      <c r="G74" s="52" t="e">
+        <f>E74-3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H74" s="52"/>
+      <c r="I74" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="J74" s="66"/>
+      <c r="J74" s="53"/>
       <c r="K74" s="6"/>
       <c r="M74" s="5"/>
       <c r="N74" s="5"/>
@@ -3217,23 +3399,28 @@
       <c r="P74" s="5"/>
       <c r="Q74" s="5"/>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A75" s="43"/>
-      <c r="B75" s="43" t="s">
+    <row r="75" spans="1:17" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A75" s="49"/>
+      <c r="B75" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="C75" s="42"/>
-      <c r="D75" s="12" t="s">
+      <c r="C75" s="48"/>
+      <c r="D75" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E75" s="66"/>
-      <c r="F75" s="66"/>
-      <c r="G75" s="66"/>
-      <c r="H75" s="66"/>
-      <c r="I75" s="66" t="s">
+      <c r="E75" s="78" t="s">
+        <v>277</v>
+      </c>
+      <c r="F75" s="78"/>
+      <c r="G75" s="53" t="e">
+        <f>E75-15</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H75" s="53"/>
+      <c r="I75" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="J75" s="66"/>
+      <c r="J75" s="53"/>
       <c r="K75" s="6"/>
       <c r="M75" s="5"/>
       <c r="N75" s="5"/>
@@ -3255,8 +3442,8 @@
       <c r="K76" s="6"/>
     </row>
     <row r="77" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="10" t="s">
-        <v>185</v>
+      <c r="A77" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -3270,7 +3457,7 @@
       <c r="K77" s="6"/>
     </row>
     <row r="78" spans="1:17" s="1" customFormat="1" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="10"/>
+      <c r="A78" s="7"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
       <c r="D78" s="6"/>
@@ -3283,739 +3470,802 @@
       <c r="K78" s="6"/>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A79" s="67" t="s">
-        <v>186</v>
-      </c>
-      <c r="B79" s="68"/>
-      <c r="C79" s="12" t="s">
+      <c r="A79" s="79" t="s">
+        <v>185</v>
+      </c>
+      <c r="B79" s="80"/>
+      <c r="C79" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D79" s="12" t="s">
+      <c r="D79" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E79" s="67" t="s">
+      <c r="E79" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="F79" s="68"/>
-      <c r="G79" s="67" t="s">
+      <c r="F79" s="80"/>
+      <c r="G79" s="79" t="s">
         <v>155</v>
       </c>
-      <c r="H79" s="68"/>
-      <c r="I79" s="66" t="s">
+      <c r="H79" s="80"/>
+      <c r="I79" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="J79" s="66"/>
+      <c r="J79" s="53"/>
       <c r="K79" s="6"/>
     </row>
     <row r="80" spans="1:17" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A80" s="89" t="s">
+      <c r="A80" s="101" t="s">
         <v>58</v>
       </c>
-      <c r="B80" s="90"/>
-      <c r="C80" s="12" t="s">
+      <c r="B80" s="102"/>
+      <c r="C80" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D80" s="11" t="s">
+      <c r="D80" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="E80" s="103" t="s">
-        <v>222</v>
-      </c>
-      <c r="F80" s="103"/>
-      <c r="G80" s="66"/>
-      <c r="H80" s="66"/>
-      <c r="I80" s="66" t="s">
+      <c r="E80" s="100" t="s">
+        <v>278</v>
+      </c>
+      <c r="F80" s="100"/>
+      <c r="G80" s="53"/>
+      <c r="H80" s="53"/>
+      <c r="I80" s="53" t="s">
         <v>120</v>
       </c>
-      <c r="J80" s="66"/>
+      <c r="J80" s="53"/>
       <c r="K80" s="6"/>
     </row>
     <row r="81" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A81" s="89" t="s">
+      <c r="A81" s="101" t="s">
         <v>57</v>
       </c>
-      <c r="B81" s="90"/>
-      <c r="C81" s="12" t="s">
+      <c r="B81" s="102"/>
+      <c r="C81" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="D81" s="11" t="s">
+      <c r="D81" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="E81" s="103" t="s">
-        <v>223</v>
-      </c>
-      <c r="F81" s="103"/>
-      <c r="G81" s="66"/>
-      <c r="H81" s="66"/>
-      <c r="I81" s="66" t="s">
+      <c r="E81" s="100" t="s">
+        <v>279</v>
+      </c>
+      <c r="F81" s="100"/>
+      <c r="G81" s="81" t="e">
+        <f>E81-10</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H81" s="82"/>
+      <c r="I81" s="53" t="s">
         <v>118</v>
       </c>
-      <c r="J81" s="66"/>
+      <c r="J81" s="53"/>
       <c r="K81" s="6"/>
     </row>
     <row r="82" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A82" s="89" t="s">
+      <c r="A82" s="101" t="s">
         <v>56</v>
       </c>
-      <c r="B82" s="90"/>
-      <c r="C82" s="12" t="s">
+      <c r="B82" s="102"/>
+      <c r="C82" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D82" s="11" t="s">
+      <c r="D82" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="E82" s="103" t="s">
-        <v>224</v>
-      </c>
-      <c r="F82" s="103"/>
-      <c r="G82" s="66"/>
-      <c r="H82" s="66"/>
-      <c r="I82" s="66" t="s">
+      <c r="E82" s="100" t="s">
+        <v>280</v>
+      </c>
+      <c r="F82" s="100"/>
+      <c r="G82" s="81" t="e">
+        <f>E82-25</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H82" s="82"/>
+      <c r="I82" s="53" t="s">
         <v>119</v>
       </c>
-      <c r="J82" s="66"/>
+      <c r="J82" s="53"/>
       <c r="K82" s="6"/>
     </row>
     <row r="83" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A83" s="89" t="s">
+      <c r="A83" s="101" t="s">
         <v>55</v>
       </c>
-      <c r="B83" s="90"/>
-      <c r="C83" s="12" t="s">
+      <c r="B83" s="102"/>
+      <c r="C83" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D83" s="11" t="s">
+      <c r="D83" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="E83" s="103" t="s">
-        <v>225</v>
-      </c>
-      <c r="F83" s="103"/>
-      <c r="G83" s="66"/>
-      <c r="H83" s="66"/>
-      <c r="I83" s="66" t="s">
+      <c r="E83" s="100" t="s">
+        <v>281</v>
+      </c>
+      <c r="F83" s="100"/>
+      <c r="G83" s="81" t="e">
+        <f>E83-50</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H83" s="82"/>
+      <c r="I83" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="J83" s="66"/>
+      <c r="J83" s="53"/>
       <c r="K83" s="6"/>
     </row>
     <row r="84" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="89" t="s">
+      <c r="A84" s="101" t="s">
         <v>54</v>
       </c>
-      <c r="B84" s="90"/>
-      <c r="C84" s="12" t="s">
+      <c r="B84" s="102"/>
+      <c r="C84" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D84" s="11" t="s">
+      <c r="D84" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="E84" s="103" t="s">
-        <v>226</v>
-      </c>
-      <c r="F84" s="103"/>
-      <c r="G84" s="66"/>
-      <c r="H84" s="66"/>
-      <c r="I84" s="66" t="s">
+      <c r="E84" s="100" t="s">
+        <v>282</v>
+      </c>
+      <c r="F84" s="100"/>
+      <c r="G84" s="81" t="e">
+        <f>E84-100</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H84" s="82"/>
+      <c r="I84" s="53" t="s">
         <v>122</v>
       </c>
-      <c r="J84" s="66"/>
+      <c r="J84" s="53"/>
       <c r="K84" s="6"/>
     </row>
     <row r="85" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A85" s="89" t="s">
+      <c r="A85" s="101" t="s">
         <v>53</v>
       </c>
-      <c r="B85" s="90"/>
-      <c r="C85" s="12" t="s">
+      <c r="B85" s="102"/>
+      <c r="C85" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D85" s="11" t="s">
+      <c r="D85" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="E85" s="103" t="s">
-        <v>227</v>
-      </c>
-      <c r="F85" s="103"/>
-      <c r="G85" s="66"/>
-      <c r="H85" s="66"/>
-      <c r="I85" s="66" t="s">
+      <c r="E85" s="100" t="s">
+        <v>283</v>
+      </c>
+      <c r="F85" s="100"/>
+      <c r="G85" s="81" t="e">
+        <f>E85-250</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H85" s="82"/>
+      <c r="I85" s="53" t="s">
         <v>123</v>
       </c>
-      <c r="J85" s="66"/>
+      <c r="J85" s="53"/>
       <c r="K85" s="6"/>
     </row>
     <row r="86" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A86" s="89" t="s">
+      <c r="A86" s="101" t="s">
         <v>52</v>
       </c>
-      <c r="B86" s="90"/>
-      <c r="C86" s="12" t="s">
+      <c r="B86" s="102"/>
+      <c r="C86" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D86" s="11" t="s">
+      <c r="D86" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="E86" s="103" t="s">
-        <v>228</v>
-      </c>
-      <c r="F86" s="103"/>
-      <c r="G86" s="66"/>
-      <c r="H86" s="66"/>
-      <c r="I86" s="66" t="s">
+      <c r="E86" s="100" t="s">
+        <v>284</v>
+      </c>
+      <c r="F86" s="100"/>
+      <c r="G86" s="81" t="e">
+        <f>E86-500</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H86" s="82"/>
+      <c r="I86" s="53" t="s">
         <v>124</v>
       </c>
-      <c r="J86" s="66"/>
+      <c r="J86" s="53"/>
       <c r="K86" s="6"/>
     </row>
     <row r="87" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A87" s="89" t="s">
+      <c r="A87" s="101" t="s">
         <v>31</v>
       </c>
-      <c r="B87" s="90"/>
-      <c r="C87" s="12" t="s">
+      <c r="B87" s="102"/>
+      <c r="C87" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D87" s="11" t="s">
+      <c r="D87" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E87" s="103" t="s">
-        <v>229</v>
-      </c>
-      <c r="F87" s="103"/>
-      <c r="G87" s="66"/>
-      <c r="H87" s="66"/>
-      <c r="I87" s="66" t="s">
+      <c r="E87" s="100" t="s">
+        <v>285</v>
+      </c>
+      <c r="F87" s="100"/>
+      <c r="G87" s="81" t="e">
+        <f>E87-1</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H87" s="82"/>
+      <c r="I87" s="53" t="s">
         <v>125</v>
       </c>
-      <c r="J87" s="66"/>
+      <c r="J87" s="53"/>
       <c r="K87" s="6"/>
     </row>
     <row r="88" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A88" s="89" t="s">
+      <c r="A88" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="B88" s="90"/>
-      <c r="C88" s="12" t="s">
+      <c r="B88" s="102"/>
+      <c r="C88" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D88" s="11" t="s">
+      <c r="D88" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="E88" s="103" t="s">
-        <v>230</v>
-      </c>
-      <c r="F88" s="103"/>
-      <c r="G88" s="66"/>
-      <c r="H88" s="66"/>
-      <c r="I88" s="66" t="s">
+      <c r="E88" s="100" t="s">
+        <v>286</v>
+      </c>
+      <c r="F88" s="100"/>
+      <c r="G88" s="81" t="e">
+        <f>E88-2.5</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H88" s="82"/>
+      <c r="I88" s="53" t="s">
         <v>126</v>
       </c>
-      <c r="J88" s="66"/>
+      <c r="J88" s="53"/>
       <c r="K88" s="6"/>
     </row>
     <row r="89" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A89" s="89" t="s">
+      <c r="A89" s="101" t="s">
         <v>33</v>
       </c>
-      <c r="B89" s="90"/>
-      <c r="C89" s="12" t="s">
+      <c r="B89" s="102"/>
+      <c r="C89" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D89" s="11" t="s">
+      <c r="D89" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="E89" s="103" t="s">
-        <v>231</v>
-      </c>
-      <c r="F89" s="103"/>
-      <c r="G89" s="66"/>
-      <c r="H89" s="66"/>
-      <c r="I89" s="66" t="s">
+      <c r="E89" s="100" t="s">
+        <v>287</v>
+      </c>
+      <c r="F89" s="100"/>
+      <c r="G89" s="81" t="e">
+        <f>E89-5</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H89" s="82"/>
+      <c r="I89" s="53" t="s">
         <v>127</v>
       </c>
-      <c r="J89" s="66"/>
+      <c r="J89" s="53"/>
       <c r="K89" s="6"/>
     </row>
     <row r="90" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A90" s="89" t="s">
+      <c r="A90" s="101" t="s">
         <v>34</v>
       </c>
-      <c r="B90" s="90"/>
-      <c r="C90" s="12" t="s">
+      <c r="B90" s="102"/>
+      <c r="C90" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D90" s="11" t="s">
+      <c r="D90" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E90" s="103" t="s">
-        <v>232</v>
-      </c>
-      <c r="F90" s="103"/>
-      <c r="G90" s="66"/>
-      <c r="H90" s="66"/>
-      <c r="I90" s="66" t="s">
+      <c r="E90" s="100" t="s">
+        <v>288</v>
+      </c>
+      <c r="F90" s="100"/>
+      <c r="G90" s="81" t="e">
+        <f t="shared" ref="G90:G99" si="0">E90-10</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H90" s="82"/>
+      <c r="I90" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="J90" s="66"/>
+      <c r="J90" s="53"/>
       <c r="K90" s="6"/>
     </row>
     <row r="91" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A91" s="89" t="s">
+      <c r="A91" s="101" t="s">
         <v>35</v>
       </c>
-      <c r="B91" s="90"/>
-      <c r="C91" s="12" t="s">
+      <c r="B91" s="102"/>
+      <c r="C91" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D91" s="11" t="s">
+      <c r="D91" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="E91" s="103" t="s">
-        <v>233</v>
-      </c>
-      <c r="F91" s="103"/>
-      <c r="G91" s="66"/>
-      <c r="H91" s="66"/>
-      <c r="I91" s="66" t="s">
+      <c r="E91" s="100" t="s">
+        <v>289</v>
+      </c>
+      <c r="F91" s="100"/>
+      <c r="G91" s="81" t="e">
+        <f>E91-25</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H91" s="82"/>
+      <c r="I91" s="53" t="s">
         <v>129</v>
       </c>
-      <c r="J91" s="66"/>
+      <c r="J91" s="53"/>
       <c r="K91" s="6"/>
     </row>
     <row r="92" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A92" s="89" t="s">
+      <c r="A92" s="101" t="s">
         <v>36</v>
       </c>
-      <c r="B92" s="90"/>
-      <c r="C92" s="12" t="s">
+      <c r="B92" s="102"/>
+      <c r="C92" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D92" s="11" t="s">
+      <c r="D92" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="E92" s="103" t="s">
-        <v>234</v>
-      </c>
-      <c r="F92" s="103"/>
-      <c r="G92" s="66"/>
-      <c r="H92" s="66"/>
-      <c r="I92" s="66" t="s">
+      <c r="E92" s="100" t="s">
+        <v>290</v>
+      </c>
+      <c r="F92" s="100"/>
+      <c r="G92" s="81" t="e">
+        <f>E92-50</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H92" s="82"/>
+      <c r="I92" s="53" t="s">
         <v>130</v>
       </c>
-      <c r="J92" s="66"/>
+      <c r="J92" s="53"/>
       <c r="K92" s="6"/>
     </row>
     <row r="93" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A93" s="89" t="s">
+      <c r="A93" s="101" t="s">
         <v>37</v>
       </c>
-      <c r="B93" s="90"/>
-      <c r="C93" s="12" t="s">
+      <c r="B93" s="102"/>
+      <c r="C93" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D93" s="11" t="s">
+      <c r="D93" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="E93" s="103" t="s">
-        <v>235</v>
-      </c>
-      <c r="F93" s="103"/>
-      <c r="G93" s="66"/>
-      <c r="H93" s="66"/>
-      <c r="I93" s="66" t="s">
+      <c r="E93" s="100" t="s">
+        <v>291</v>
+      </c>
+      <c r="F93" s="100"/>
+      <c r="G93" s="81" t="e">
+        <f>E93-100</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H93" s="82"/>
+      <c r="I93" s="53" t="s">
         <v>131</v>
       </c>
-      <c r="J93" s="66"/>
+      <c r="J93" s="53"/>
       <c r="K93" s="6"/>
     </row>
     <row r="94" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A94" s="89" t="s">
+      <c r="A94" s="101" t="s">
         <v>38</v>
       </c>
-      <c r="B94" s="90"/>
-      <c r="C94" s="12" t="s">
+      <c r="B94" s="102"/>
+      <c r="C94" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D94" s="11" t="s">
+      <c r="D94" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="E94" s="103" t="s">
-        <v>236</v>
-      </c>
-      <c r="F94" s="103"/>
-      <c r="G94" s="66"/>
-      <c r="H94" s="66"/>
-      <c r="I94" s="66" t="s">
+      <c r="E94" s="100" t="s">
+        <v>292</v>
+      </c>
+      <c r="F94" s="100"/>
+      <c r="G94" s="81" t="e">
+        <f>E94-250</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H94" s="82"/>
+      <c r="I94" s="53" t="s">
         <v>132</v>
       </c>
-      <c r="J94" s="66"/>
+      <c r="J94" s="53"/>
       <c r="K94" s="6"/>
     </row>
     <row r="95" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A95" s="89" t="s">
+      <c r="A95" s="101" t="s">
         <v>39</v>
       </c>
-      <c r="B95" s="90"/>
-      <c r="C95" s="12" t="s">
+      <c r="B95" s="102"/>
+      <c r="C95" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="D95" s="11" t="s">
+      <c r="D95" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="E95" s="103" t="s">
-        <v>237</v>
-      </c>
-      <c r="F95" s="103"/>
-      <c r="G95" s="66"/>
-      <c r="H95" s="66"/>
-      <c r="I95" s="66" t="s">
+      <c r="E95" s="100" t="s">
+        <v>293</v>
+      </c>
+      <c r="F95" s="100"/>
+      <c r="G95" s="81" t="e">
+        <f>E95-500</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H95" s="82"/>
+      <c r="I95" s="53" t="s">
         <v>133</v>
       </c>
-      <c r="J95" s="66"/>
+      <c r="J95" s="53"/>
       <c r="K95" s="6"/>
     </row>
     <row r="96" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A96" s="89" t="s">
+      <c r="A96" s="101" t="s">
         <v>40</v>
       </c>
-      <c r="B96" s="90"/>
-      <c r="C96" s="12" t="s">
+      <c r="B96" s="102"/>
+      <c r="C96" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D96" s="11" t="s">
+      <c r="D96" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="E96" s="103" t="s">
-        <v>238</v>
-      </c>
-      <c r="F96" s="103"/>
-      <c r="G96" s="66"/>
-      <c r="H96" s="66"/>
-      <c r="I96" s="66" t="s">
+      <c r="E96" s="100" t="s">
+        <v>294</v>
+      </c>
+      <c r="F96" s="100"/>
+      <c r="G96" s="81" t="e">
+        <f>E96-1</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H96" s="82"/>
+      <c r="I96" s="53" t="s">
         <v>134</v>
       </c>
-      <c r="J96" s="66"/>
+      <c r="J96" s="53"/>
       <c r="K96" s="6"/>
     </row>
     <row r="97" spans="1:17" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A97" s="89" t="s">
+      <c r="A97" s="101" t="s">
         <v>41</v>
       </c>
-      <c r="B97" s="90"/>
-      <c r="C97" s="12" t="s">
+      <c r="B97" s="102"/>
+      <c r="C97" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D97" s="11" t="s">
+      <c r="D97" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E97" s="103" t="s">
-        <v>239</v>
-      </c>
-      <c r="F97" s="103"/>
-      <c r="G97" s="66"/>
-      <c r="H97" s="66"/>
-      <c r="I97" s="66" t="s">
+      <c r="E97" s="100" t="s">
+        <v>295</v>
+      </c>
+      <c r="F97" s="100"/>
+      <c r="G97" s="81" t="e">
+        <f>E97-2.5</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H97" s="82"/>
+      <c r="I97" s="53" t="s">
         <v>135</v>
       </c>
-      <c r="J97" s="66"/>
+      <c r="J97" s="53"/>
       <c r="K97" s="6"/>
-      <c r="L97" s="17"/>
-      <c r="M97" s="17"/>
+      <c r="L97" s="14"/>
+      <c r="M97" s="14"/>
       <c r="N97" s="5"/>
       <c r="O97" s="5"/>
-      <c r="P97" s="20"/>
-      <c r="Q97" s="20"/>
+      <c r="P97" s="17"/>
+      <c r="Q97" s="17"/>
     </row>
     <row r="98" spans="1:17" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A98" s="89" t="s">
+      <c r="A98" s="101" t="s">
         <v>42</v>
       </c>
-      <c r="B98" s="90"/>
-      <c r="C98" s="12" t="s">
+      <c r="B98" s="102"/>
+      <c r="C98" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="D98" s="11" t="s">
+      <c r="D98" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="E98" s="103" t="s">
-        <v>240</v>
-      </c>
-      <c r="F98" s="103"/>
-      <c r="G98" s="66"/>
-      <c r="H98" s="66"/>
-      <c r="I98" s="66" t="s">
+      <c r="E98" s="100" t="s">
+        <v>296</v>
+      </c>
+      <c r="F98" s="100"/>
+      <c r="G98" s="81" t="e">
+        <f>E98-5</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H98" s="82"/>
+      <c r="I98" s="53" t="s">
         <v>136</v>
       </c>
-      <c r="J98" s="66"/>
+      <c r="J98" s="53"/>
       <c r="K98" s="6"/>
       <c r="L98" s="5"/>
       <c r="M98" s="5"/>
-      <c r="N98" s="21"/>
+      <c r="N98" s="18"/>
       <c r="O98" s="5"/>
-      <c r="P98" s="20"/>
-      <c r="Q98" s="20"/>
+      <c r="P98" s="17"/>
+      <c r="Q98" s="17"/>
     </row>
     <row r="99" spans="1:17" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="89" t="s">
+      <c r="A99" s="101" t="s">
         <v>43</v>
       </c>
-      <c r="B99" s="90"/>
-      <c r="C99" s="12" t="s">
+      <c r="B99" s="102"/>
+      <c r="C99" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D99" s="11" t="s">
+      <c r="D99" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="E99" s="103" t="s">
-        <v>241</v>
-      </c>
-      <c r="F99" s="103"/>
-      <c r="G99" s="66"/>
-      <c r="H99" s="66"/>
-      <c r="I99" s="66" t="s">
+      <c r="E99" s="100" t="s">
+        <v>297</v>
+      </c>
+      <c r="F99" s="100"/>
+      <c r="G99" s="81" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H99" s="82"/>
+      <c r="I99" s="53" t="s">
         <v>137</v>
       </c>
-      <c r="J99" s="66"/>
+      <c r="J99" s="53"/>
       <c r="K99" s="6"/>
       <c r="L99" s="5"/>
       <c r="M99" s="5"/>
       <c r="N99" s="5"/>
       <c r="O99" s="5"/>
-      <c r="P99" s="20"/>
-      <c r="Q99" s="20"/>
+      <c r="P99" s="17"/>
+      <c r="Q99" s="17"/>
     </row>
     <row r="100" spans="1:17" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A100" s="89" t="s">
+      <c r="A100" s="101" t="s">
         <v>44</v>
       </c>
-      <c r="B100" s="90"/>
-      <c r="C100" s="12" t="s">
+      <c r="B100" s="102"/>
+      <c r="C100" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="D100" s="11" t="s">
+      <c r="D100" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="E100" s="103" t="s">
-        <v>242</v>
-      </c>
-      <c r="F100" s="103"/>
-      <c r="G100" s="66"/>
-      <c r="H100" s="66"/>
-      <c r="I100" s="66" t="s">
+      <c r="E100" s="100" t="s">
+        <v>298</v>
+      </c>
+      <c r="F100" s="100"/>
+      <c r="G100" s="81" t="e">
+        <f>E100-25</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H100" s="82"/>
+      <c r="I100" s="53" t="s">
         <v>138</v>
       </c>
-      <c r="J100" s="66"/>
+      <c r="J100" s="53"/>
       <c r="K100" s="6"/>
       <c r="L100" s="5"/>
       <c r="M100" s="5"/>
       <c r="N100" s="5"/>
       <c r="O100" s="5"/>
-      <c r="P100" s="20"/>
-      <c r="Q100" s="20"/>
+      <c r="P100" s="17"/>
+      <c r="Q100" s="17"/>
     </row>
     <row r="101" spans="1:17" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A101" s="89" t="s">
+      <c r="A101" s="101" t="s">
         <v>45</v>
       </c>
-      <c r="B101" s="90"/>
-      <c r="C101" s="12" t="s">
+      <c r="B101" s="102"/>
+      <c r="C101" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="D101" s="11" t="s">
+      <c r="D101" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="E101" s="103" t="s">
-        <v>243</v>
-      </c>
-      <c r="F101" s="103"/>
-      <c r="G101" s="66"/>
-      <c r="H101" s="66"/>
-      <c r="I101" s="66" t="s">
+      <c r="E101" s="100" t="s">
+        <v>299</v>
+      </c>
+      <c r="F101" s="100"/>
+      <c r="G101" s="81" t="e">
+        <f>E101-50</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H101" s="82"/>
+      <c r="I101" s="53" t="s">
         <v>139</v>
       </c>
-      <c r="J101" s="66"/>
+      <c r="J101" s="53"/>
       <c r="K101" s="6"/>
       <c r="L101" s="5"/>
       <c r="M101" s="5"/>
       <c r="N101" s="5"/>
       <c r="O101" s="5"/>
-      <c r="P101" s="20"/>
-      <c r="Q101" s="20"/>
+      <c r="P101" s="17"/>
+      <c r="Q101" s="17"/>
     </row>
     <row r="102" spans="1:17" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A102" s="89" t="s">
+      <c r="A102" s="101" t="s">
         <v>46</v>
       </c>
-      <c r="B102" s="90"/>
-      <c r="C102" s="12" t="s">
+      <c r="B102" s="102"/>
+      <c r="C102" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D102" s="11" t="s">
+      <c r="D102" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="E102" s="103" t="s">
-        <v>244</v>
-      </c>
-      <c r="F102" s="103"/>
-      <c r="G102" s="66"/>
-      <c r="H102" s="66"/>
-      <c r="I102" s="66" t="s">
+      <c r="E102" s="100" t="s">
+        <v>300</v>
+      </c>
+      <c r="F102" s="100"/>
+      <c r="G102" s="53"/>
+      <c r="H102" s="53"/>
+      <c r="I102" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="J102" s="66"/>
+      <c r="J102" s="53"/>
       <c r="K102" s="6"/>
       <c r="L102" s="5"/>
       <c r="M102" s="5"/>
       <c r="N102" s="5"/>
       <c r="O102" s="5"/>
-      <c r="P102" s="20"/>
-      <c r="Q102" s="20"/>
+      <c r="P102" s="17"/>
+      <c r="Q102" s="17"/>
     </row>
     <row r="103" spans="1:17" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A103" s="89" t="s">
+      <c r="A103" s="101" t="s">
         <v>47</v>
       </c>
-      <c r="B103" s="90"/>
-      <c r="C103" s="12" t="s">
+      <c r="B103" s="102"/>
+      <c r="C103" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="D103" s="11" t="s">
+      <c r="D103" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="E103" s="103" t="s">
-        <v>245</v>
-      </c>
-      <c r="F103" s="103"/>
-      <c r="G103" s="66"/>
-      <c r="H103" s="66"/>
-      <c r="I103" s="66" t="s">
+      <c r="E103" s="100" t="s">
+        <v>301</v>
+      </c>
+      <c r="F103" s="100"/>
+      <c r="G103" s="53"/>
+      <c r="H103" s="53"/>
+      <c r="I103" s="53" t="s">
         <v>141</v>
       </c>
-      <c r="J103" s="66"/>
+      <c r="J103" s="53"/>
       <c r="K103" s="6"/>
       <c r="L103" s="5"/>
       <c r="M103" s="5"/>
       <c r="N103" s="5"/>
       <c r="O103" s="5"/>
-      <c r="P103" s="20"/>
-      <c r="Q103" s="20"/>
+      <c r="P103" s="17"/>
+      <c r="Q103" s="17"/>
     </row>
     <row r="104" spans="1:17" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A104" s="89" t="s">
+      <c r="A104" s="101" t="s">
         <v>48</v>
       </c>
-      <c r="B104" s="90"/>
-      <c r="C104" s="12" t="s">
+      <c r="B104" s="102"/>
+      <c r="C104" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="11" t="s">
+      <c r="D104" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="E104" s="103" t="s">
-        <v>246</v>
-      </c>
-      <c r="F104" s="103"/>
-      <c r="G104" s="66"/>
-      <c r="H104" s="66"/>
-      <c r="I104" s="66" t="s">
+      <c r="E104" s="100" t="s">
+        <v>302</v>
+      </c>
+      <c r="F104" s="100"/>
+      <c r="G104" s="53"/>
+      <c r="H104" s="53"/>
+      <c r="I104" s="53" t="s">
         <v>142</v>
       </c>
-      <c r="J104" s="66"/>
+      <c r="J104" s="53"/>
       <c r="K104" s="6"/>
       <c r="L104" s="5"/>
       <c r="M104" s="5"/>
       <c r="N104" s="5"/>
       <c r="O104" s="5"/>
-      <c r="P104" s="20"/>
-      <c r="Q104" s="20"/>
+      <c r="P104" s="17"/>
+      <c r="Q104" s="17"/>
     </row>
     <row r="105" spans="1:17" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A105" s="89" t="s">
+      <c r="A105" s="101" t="s">
         <v>49</v>
       </c>
-      <c r="B105" s="90"/>
-      <c r="C105" s="12" t="s">
+      <c r="B105" s="102"/>
+      <c r="C105" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="D105" s="11" t="s">
+      <c r="D105" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="E105" s="103" t="s">
-        <v>247</v>
-      </c>
-      <c r="F105" s="103"/>
-      <c r="G105" s="66"/>
-      <c r="H105" s="66"/>
-      <c r="I105" s="66" t="s">
+      <c r="E105" s="100" t="s">
+        <v>303</v>
+      </c>
+      <c r="F105" s="100"/>
+      <c r="G105" s="53"/>
+      <c r="H105" s="53"/>
+      <c r="I105" s="53" t="s">
         <v>144</v>
       </c>
-      <c r="J105" s="66"/>
+      <c r="J105" s="53"/>
       <c r="K105" s="6"/>
       <c r="L105" s="5"/>
       <c r="M105" s="5"/>
       <c r="N105" s="5"/>
       <c r="O105" s="5"/>
-      <c r="P105" s="20"/>
-      <c r="Q105" s="20"/>
+      <c r="P105" s="17"/>
+      <c r="Q105" s="17"/>
     </row>
     <row r="106" spans="1:17" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A106" s="89" t="s">
+      <c r="A106" s="101" t="s">
         <v>50</v>
       </c>
-      <c r="B106" s="90"/>
-      <c r="C106" s="12" t="s">
+      <c r="B106" s="102"/>
+      <c r="C106" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="D106" s="11" t="s">
+      <c r="D106" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="E106" s="103" t="s">
-        <v>248</v>
-      </c>
-      <c r="F106" s="103"/>
-      <c r="G106" s="66"/>
-      <c r="H106" s="66"/>
-      <c r="I106" s="66" t="s">
+      <c r="E106" s="100" t="s">
+        <v>304</v>
+      </c>
+      <c r="F106" s="100"/>
+      <c r="G106" s="53"/>
+      <c r="H106" s="53"/>
+      <c r="I106" s="53" t="s">
         <v>145</v>
       </c>
-      <c r="J106" s="66"/>
+      <c r="J106" s="53"/>
       <c r="K106" s="6"/>
       <c r="L106" s="5"/>
       <c r="M106" s="5"/>
       <c r="N106" s="5"/>
       <c r="O106" s="5"/>
-      <c r="P106" s="20"/>
-      <c r="Q106" s="20"/>
+      <c r="P106" s="17"/>
+      <c r="Q106" s="17"/>
     </row>
     <row r="107" spans="1:17" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A107" s="89" t="s">
+      <c r="A107" s="101" t="s">
         <v>51</v>
       </c>
-      <c r="B107" s="90"/>
-      <c r="C107" s="12" t="s">
+      <c r="B107" s="102"/>
+      <c r="C107" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="D107" s="11" t="s">
+      <c r="D107" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="E107" s="103" t="s">
-        <v>249</v>
-      </c>
-      <c r="F107" s="103"/>
-      <c r="G107" s="66"/>
-      <c r="H107" s="66"/>
-      <c r="I107" s="66" t="s">
+      <c r="E107" s="100" t="s">
+        <v>305</v>
+      </c>
+      <c r="F107" s="100"/>
+      <c r="G107" s="53"/>
+      <c r="H107" s="53"/>
+      <c r="I107" s="53" t="s">
         <v>143</v>
       </c>
-      <c r="J107" s="66"/>
+      <c r="J107" s="53"/>
       <c r="K107" s="6"/>
       <c r="L107" s="5"/>
       <c r="M107" s="5"/>
       <c r="N107" s="5"/>
       <c r="O107" s="5"/>
-      <c r="P107" s="20"/>
-      <c r="Q107" s="20"/>
+      <c r="P107" s="17"/>
+      <c r="Q107" s="17"/>
     </row>
     <row r="108" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="2"/>
@@ -4033,12 +4283,12 @@
       <c r="M108" s="5"/>
       <c r="N108" s="5"/>
       <c r="O108" s="5"/>
-      <c r="P108" s="20"/>
-      <c r="Q108" s="20"/>
+      <c r="P108" s="17"/>
+      <c r="Q108" s="17"/>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A109" s="10" t="s">
-        <v>187</v>
+      <c r="A109" s="7" t="s">
+        <v>186</v>
       </c>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -4054,11 +4304,11 @@
       <c r="M109" s="5"/>
       <c r="N109" s="5"/>
       <c r="O109" s="5"/>
-      <c r="P109" s="20"/>
-      <c r="Q109" s="20"/>
+      <c r="P109" s="17"/>
+      <c r="Q109" s="17"/>
     </row>
     <row r="110" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="10"/>
+      <c r="A110" s="7"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
       <c r="D110" s="2"/>
@@ -4073,25 +4323,25 @@
       <c r="M110" s="5"/>
       <c r="N110" s="5"/>
       <c r="O110" s="5"/>
-      <c r="P110" s="20"/>
-      <c r="Q110" s="20"/>
+      <c r="P110" s="17"/>
+      <c r="Q110" s="17"/>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A111" s="43" t="s">
-        <v>184</v>
-      </c>
-      <c r="B111" s="41" t="s">
+      <c r="A111" s="49" t="s">
+        <v>183</v>
+      </c>
+      <c r="B111" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C111" s="41"/>
-      <c r="D111" s="61" t="s">
+      <c r="C111" s="47"/>
+      <c r="D111" s="73" t="s">
         <v>150</v>
       </c>
-      <c r="E111" s="43" t="s">
+      <c r="E111" s="49" t="s">
         <v>149</v>
       </c>
-      <c r="F111" s="43"/>
-      <c r="G111" s="43"/>
+      <c r="F111" s="49"/>
+      <c r="G111" s="49"/>
       <c r="H111" s="2"/>
       <c r="I111" s="2"/>
       <c r="J111" s="2"/>
@@ -4104,10 +4354,10 @@
       <c r="Q111" s="5"/>
     </row>
     <row r="112" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="43"/>
-      <c r="B112" s="41"/>
-      <c r="C112" s="41"/>
-      <c r="D112" s="61"/>
+      <c r="A112" s="49"/>
+      <c r="B112" s="47"/>
+      <c r="C112" s="47"/>
+      <c r="D112" s="73"/>
       <c r="E112" s="4" t="s">
         <v>146</v>
       </c>
@@ -4123,23 +4373,23 @@
       <c r="K112" s="2"/>
     </row>
     <row r="113" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A113" s="43" t="s">
+      <c r="A113" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="B113" s="41" t="s">
+      <c r="B113" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="C113" s="43"/>
-      <c r="D113" s="100" t="s">
-        <v>216</v>
-      </c>
-      <c r="E113" s="58">
+      <c r="C113" s="49"/>
+      <c r="D113" s="43" t="s">
+        <v>203</v>
+      </c>
+      <c r="E113" s="70">
         <v>5.85</v>
       </c>
-      <c r="F113" s="58">
+      <c r="F113" s="70">
         <v>3.5</v>
       </c>
-      <c r="G113" s="58">
+      <c r="G113" s="70">
         <v>3.5</v>
       </c>
       <c r="H113" s="2"/>
@@ -4148,181 +4398,193 @@
       <c r="K113" s="2"/>
     </row>
     <row r="114" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A114" s="43"/>
-      <c r="B114" s="41" t="s">
+      <c r="A114" s="49"/>
+      <c r="B114" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="C114" s="43"/>
-      <c r="D114" s="100" t="s">
-        <v>217</v>
-      </c>
-      <c r="E114" s="59"/>
-      <c r="F114" s="59"/>
-      <c r="G114" s="59"/>
+      <c r="C114" s="49"/>
+      <c r="D114" s="43" t="s">
+        <v>204</v>
+      </c>
+      <c r="E114" s="71"/>
+      <c r="F114" s="71"/>
+      <c r="G114" s="71"/>
       <c r="H114" s="2"/>
       <c r="I114" s="2"/>
       <c r="J114" s="2"/>
       <c r="K114" s="2"/>
     </row>
     <row r="115" spans="1:11" ht="14.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="63"/>
-      <c r="B115" s="63" t="s">
+      <c r="A115" s="75"/>
+      <c r="B115" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="C115" s="63"/>
-      <c r="D115" s="102" t="s">
-        <v>218</v>
-      </c>
-      <c r="E115" s="59"/>
-      <c r="F115" s="59"/>
-      <c r="G115" s="59"/>
+      <c r="C115" s="75"/>
+      <c r="D115" s="44" t="s">
+        <v>205</v>
+      </c>
+      <c r="E115" s="71"/>
+      <c r="F115" s="71"/>
+      <c r="G115" s="71"/>
       <c r="H115" s="2"/>
       <c r="I115" s="2"/>
       <c r="J115" s="2"/>
       <c r="K115" s="2"/>
     </row>
     <row r="116" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A116" s="64" t="s">
+      <c r="A116" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="B116" s="65" t="s">
+      <c r="B116" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="C116" s="64"/>
-      <c r="D116" s="101" t="s">
-        <v>219</v>
-      </c>
-      <c r="E116" s="59"/>
-      <c r="F116" s="59"/>
-      <c r="G116" s="59"/>
+      <c r="C116" s="76"/>
+      <c r="D116" s="45" t="s">
+        <v>206</v>
+      </c>
+      <c r="E116" s="71"/>
+      <c r="F116" s="71"/>
+      <c r="G116" s="71"/>
       <c r="H116" s="2"/>
       <c r="I116" s="2"/>
       <c r="J116" s="2"/>
       <c r="K116" s="2"/>
     </row>
     <row r="117" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A117" s="43"/>
-      <c r="B117" s="41" t="s">
+      <c r="A117" s="49"/>
+      <c r="B117" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="C117" s="43"/>
-      <c r="D117" s="100" t="s">
-        <v>220</v>
-      </c>
-      <c r="E117" s="59"/>
-      <c r="F117" s="59"/>
-      <c r="G117" s="59"/>
+      <c r="C117" s="49"/>
+      <c r="D117" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="E117" s="71"/>
+      <c r="F117" s="71"/>
+      <c r="G117" s="71"/>
       <c r="H117" s="2"/>
       <c r="I117" s="2"/>
       <c r="J117" s="2"/>
       <c r="K117" s="2"/>
     </row>
     <row r="118" spans="1:11" ht="14.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="63"/>
-      <c r="B118" s="63" t="s">
+      <c r="A118" s="75"/>
+      <c r="B118" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="C118" s="63"/>
-      <c r="D118" s="100" t="s">
-        <v>221</v>
-      </c>
-      <c r="E118" s="59"/>
-      <c r="F118" s="59"/>
-      <c r="G118" s="59"/>
+      <c r="C118" s="75"/>
+      <c r="D118" s="44" t="s">
+        <v>208</v>
+      </c>
+      <c r="E118" s="71"/>
+      <c r="F118" s="71"/>
+      <c r="G118" s="71"/>
       <c r="H118" s="2"/>
       <c r="I118" s="2"/>
       <c r="J118" s="2"/>
       <c r="K118" s="2"/>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A119" s="64" t="s">
+    <row r="119" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A119" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="B119" s="65" t="s">
+      <c r="B119" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="C119" s="64"/>
-      <c r="D119" s="7"/>
-      <c r="E119" s="59"/>
-      <c r="F119" s="59"/>
-      <c r="G119" s="59"/>
+      <c r="C119" s="76"/>
+      <c r="D119" s="45" t="s">
+        <v>222</v>
+      </c>
+      <c r="E119" s="71"/>
+      <c r="F119" s="71"/>
+      <c r="G119" s="71"/>
       <c r="H119" s="2"/>
       <c r="I119" s="2"/>
       <c r="J119" s="2"/>
       <c r="K119" s="2"/>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A120" s="43"/>
-      <c r="B120" s="41" t="s">
+    <row r="120" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A120" s="49"/>
+      <c r="B120" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="C120" s="43"/>
-      <c r="D120" s="4"/>
-      <c r="E120" s="59"/>
-      <c r="F120" s="59"/>
-      <c r="G120" s="59"/>
+      <c r="C120" s="49"/>
+      <c r="D120" s="45" t="s">
+        <v>224</v>
+      </c>
+      <c r="E120" s="71"/>
+      <c r="F120" s="71"/>
+      <c r="G120" s="71"/>
       <c r="H120" s="2"/>
       <c r="I120" s="2"/>
       <c r="J120" s="2"/>
       <c r="K120" s="2"/>
     </row>
-    <row r="121" spans="1:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="63"/>
-      <c r="B121" s="63" t="s">
+    <row r="121" spans="1:11" ht="14.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="75"/>
+      <c r="B121" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="C121" s="63"/>
-      <c r="D121" s="8"/>
-      <c r="E121" s="59"/>
-      <c r="F121" s="59"/>
-      <c r="G121" s="59"/>
+      <c r="C121" s="75"/>
+      <c r="D121" s="44" t="s">
+        <v>225</v>
+      </c>
+      <c r="E121" s="71"/>
+      <c r="F121" s="71"/>
+      <c r="G121" s="71"/>
       <c r="H121" s="2"/>
       <c r="I121" s="2"/>
       <c r="J121" s="2"/>
       <c r="K121" s="2"/>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A122" s="60" t="s">
+    <row r="122" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A122" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="B122" s="62" t="s">
+      <c r="B122" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="C122" s="60"/>
-      <c r="D122" s="9"/>
-      <c r="E122" s="59"/>
-      <c r="F122" s="59"/>
-      <c r="G122" s="59"/>
+      <c r="C122" s="72"/>
+      <c r="D122" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="E122" s="71"/>
+      <c r="F122" s="71"/>
+      <c r="G122" s="71"/>
       <c r="H122" s="2"/>
       <c r="I122" s="2"/>
       <c r="J122" s="2"/>
       <c r="K122" s="2"/>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A123" s="43"/>
-      <c r="B123" s="41" t="s">
+    <row r="123" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A123" s="49"/>
+      <c r="B123" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="C123" s="43"/>
-      <c r="D123" s="4"/>
-      <c r="E123" s="59"/>
-      <c r="F123" s="59"/>
-      <c r="G123" s="59"/>
+      <c r="C123" s="49"/>
+      <c r="D123" s="45" t="s">
+        <v>226</v>
+      </c>
+      <c r="E123" s="71"/>
+      <c r="F123" s="71"/>
+      <c r="G123" s="71"/>
       <c r="H123" s="2"/>
       <c r="I123" s="2"/>
       <c r="J123" s="2"/>
       <c r="K123" s="2"/>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A124" s="43"/>
-      <c r="B124" s="43" t="s">
+    <row r="124" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A124" s="49"/>
+      <c r="B124" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="C124" s="43"/>
-      <c r="D124" s="4"/>
-      <c r="E124" s="60"/>
-      <c r="F124" s="60"/>
-      <c r="G124" s="60"/>
+      <c r="C124" s="49"/>
+      <c r="D124" s="45" t="s">
+        <v>227</v>
+      </c>
+      <c r="E124" s="72"/>
+      <c r="F124" s="72"/>
+      <c r="G124" s="72"/>
       <c r="H124" s="2"/>
       <c r="I124" s="2"/>
       <c r="J124" s="2"/>
@@ -4341,45 +4603,45 @@
       <c r="J125" s="2"/>
       <c r="K125" s="2"/>
     </row>
-    <row r="126" spans="1:11" s="107" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A126" s="104" t="s">
-        <v>250</v>
-      </c>
-      <c r="B126" s="104"/>
-      <c r="C126" s="105"/>
+    <row r="126" spans="1:11" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A126" s="103" t="s">
+        <v>209</v>
+      </c>
+      <c r="B126" s="103"/>
+      <c r="C126" s="37"/>
       <c r="D126" s="6"/>
       <c r="E126" s="6"/>
-      <c r="F126" s="106"/>
+      <c r="F126" s="38"/>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
     </row>
-    <row r="127" spans="1:11" s="107" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A127" s="104" t="s">
-        <v>251</v>
-      </c>
-      <c r="B127" s="104"/>
-      <c r="C127" s="108"/>
-      <c r="D127" s="109" t="s">
-        <v>252</v>
-      </c>
-      <c r="E127" s="110" t="s">
-        <v>253</v>
-      </c>
-      <c r="F127" s="111"/>
+    <row r="127" spans="1:11" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A127" s="103" t="s">
+        <v>210</v>
+      </c>
+      <c r="B127" s="103"/>
+      <c r="C127" s="40"/>
+      <c r="D127" s="41" t="s">
+        <v>211</v>
+      </c>
+      <c r="E127" s="104" t="s">
+        <v>212</v>
+      </c>
+      <c r="F127" s="105"/>
       <c r="G127" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="H127" s="112"/>
-    </row>
-    <row r="128" spans="1:11" s="107" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A128" s="104" t="s">
-        <v>255</v>
-      </c>
-      <c r="B128" s="104"/>
-      <c r="C128" s="113" t="s">
-        <v>256</v>
-      </c>
-      <c r="D128" s="113"/>
+        <v>213</v>
+      </c>
+      <c r="H127" s="42"/>
+    </row>
+    <row r="128" spans="1:11" s="39" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A128" s="103" t="s">
+        <v>214</v>
+      </c>
+      <c r="B128" s="103"/>
+      <c r="C128" s="106" t="s">
+        <v>215</v>
+      </c>
+      <c r="D128" s="106"/>
       <c r="E128" s="2"/>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
@@ -4474,17 +4736,6 @@
     <mergeCell ref="A104:B104"/>
     <mergeCell ref="A103:B103"/>
     <mergeCell ref="A102:B102"/>
-    <mergeCell ref="E107:F107"/>
-    <mergeCell ref="I91:J91"/>
-    <mergeCell ref="I92:J92"/>
-    <mergeCell ref="I93:J93"/>
-    <mergeCell ref="I94:J94"/>
-    <mergeCell ref="I95:J95"/>
-    <mergeCell ref="I96:J96"/>
-    <mergeCell ref="I97:J97"/>
-    <mergeCell ref="I98:J98"/>
-    <mergeCell ref="I99:J99"/>
-    <mergeCell ref="I104:J104"/>
     <mergeCell ref="I105:J105"/>
     <mergeCell ref="I106:J106"/>
     <mergeCell ref="I107:J107"/>
@@ -4498,49 +4749,49 @@
     <mergeCell ref="E94:F94"/>
     <mergeCell ref="E103:F103"/>
     <mergeCell ref="E104:F104"/>
+    <mergeCell ref="I91:J91"/>
+    <mergeCell ref="I92:J92"/>
+    <mergeCell ref="I93:J93"/>
+    <mergeCell ref="I94:J94"/>
+    <mergeCell ref="I95:J95"/>
+    <mergeCell ref="I96:J96"/>
+    <mergeCell ref="I97:J97"/>
+    <mergeCell ref="I98:J98"/>
+    <mergeCell ref="I99:J99"/>
+    <mergeCell ref="G107:H107"/>
+    <mergeCell ref="G101:H101"/>
+    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="E88:F88"/>
+    <mergeCell ref="E89:F89"/>
+    <mergeCell ref="E90:F90"/>
+    <mergeCell ref="E97:F97"/>
+    <mergeCell ref="E98:F98"/>
+    <mergeCell ref="I104:J104"/>
+    <mergeCell ref="G105:H105"/>
+    <mergeCell ref="G106:H106"/>
+    <mergeCell ref="G103:H103"/>
+    <mergeCell ref="G104:H104"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="G90:H90"/>
+    <mergeCell ref="G91:H91"/>
+    <mergeCell ref="G92:H92"/>
     <mergeCell ref="E105:F105"/>
     <mergeCell ref="E106:F106"/>
     <mergeCell ref="E99:F99"/>
     <mergeCell ref="E100:F100"/>
     <mergeCell ref="E101:F101"/>
     <mergeCell ref="E102:F102"/>
-    <mergeCell ref="G107:H107"/>
-    <mergeCell ref="E80:F80"/>
-    <mergeCell ref="E81:F81"/>
-    <mergeCell ref="E82:F82"/>
-    <mergeCell ref="E83:F83"/>
-    <mergeCell ref="E84:F84"/>
-    <mergeCell ref="E85:F85"/>
-    <mergeCell ref="E86:F86"/>
-    <mergeCell ref="G101:H101"/>
-    <mergeCell ref="G102:H102"/>
-    <mergeCell ref="E87:F87"/>
-    <mergeCell ref="E88:F88"/>
-    <mergeCell ref="E89:F89"/>
-    <mergeCell ref="E90:F90"/>
-    <mergeCell ref="G105:H105"/>
-    <mergeCell ref="G106:H106"/>
-    <mergeCell ref="G103:H103"/>
-    <mergeCell ref="G104:H104"/>
-    <mergeCell ref="G97:H97"/>
-    <mergeCell ref="G98:H98"/>
-    <mergeCell ref="E95:F95"/>
-    <mergeCell ref="E96:F96"/>
-    <mergeCell ref="E97:F97"/>
-    <mergeCell ref="E98:F98"/>
-    <mergeCell ref="G90:H90"/>
-    <mergeCell ref="G91:H91"/>
-    <mergeCell ref="G92:H92"/>
-    <mergeCell ref="G85:H85"/>
-    <mergeCell ref="G86:H86"/>
-    <mergeCell ref="G87:H87"/>
-    <mergeCell ref="G88:H88"/>
     <mergeCell ref="G99:H99"/>
     <mergeCell ref="G100:H100"/>
     <mergeCell ref="G93:H93"/>
     <mergeCell ref="G94:H94"/>
     <mergeCell ref="G95:H95"/>
     <mergeCell ref="G96:H96"/>
+    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="G98:H98"/>
+    <mergeCell ref="E95:F95"/>
+    <mergeCell ref="E96:F96"/>
     <mergeCell ref="I53:J53"/>
     <mergeCell ref="A38:B39"/>
     <mergeCell ref="C38:D39"/>
@@ -4649,8 +4900,6 @@
     <mergeCell ref="G57:H57"/>
     <mergeCell ref="I57:J57"/>
     <mergeCell ref="E58:F58"/>
-    <mergeCell ref="G58:H58"/>
-    <mergeCell ref="I58:J58"/>
     <mergeCell ref="E64:F64"/>
     <mergeCell ref="G64:H64"/>
     <mergeCell ref="I64:J64"/>
@@ -4676,6 +4925,11 @@
     <mergeCell ref="E73:F73"/>
     <mergeCell ref="G73:H73"/>
     <mergeCell ref="I73:J73"/>
+    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="E81:F81"/>
+    <mergeCell ref="E82:F82"/>
+    <mergeCell ref="E83:F83"/>
+    <mergeCell ref="E84:F84"/>
     <mergeCell ref="I86:J86"/>
     <mergeCell ref="I87:J87"/>
     <mergeCell ref="I88:J88"/>
@@ -4688,6 +4942,12 @@
     <mergeCell ref="G80:H80"/>
     <mergeCell ref="E79:F79"/>
     <mergeCell ref="G89:H89"/>
+    <mergeCell ref="G85:H85"/>
+    <mergeCell ref="G86:H86"/>
+    <mergeCell ref="G87:H87"/>
+    <mergeCell ref="G88:H88"/>
+    <mergeCell ref="E85:F85"/>
+    <mergeCell ref="E86:F86"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A6:D6"/>
@@ -4758,6 +5018,8 @@
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="G63:H63"/>
     <mergeCell ref="I63:J63"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="I58:J58"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.78740157480314965" right="0.78740157480314965" top="0.39370078740157483" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.51181102362204722"/>
